--- a/Working_Cost_Models/TCS/ROK_TCS_CostModel_V2.xlsx
+++ b/Working_Cost_Models/TCS/ROK_TCS_CostModel_V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tricoreplumbing-my.sharepoint.com/personal/mitch_tricoreplumbing_com_au/Documents/Documents/GitHub/ROK Sports Precinct - Stage 1/Working_Cost_Models/TCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_34072D637E2912D3C9FA09EF4B45A16AFC5CED29" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_ADC74B1B7F38351349CD6DE73C5C97F7A66738FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="938">
   <si>
     <t>ROK SPORTS PRECINCT — STAGE 1  |  TCS COST MODEL V2</t>
   </si>
@@ -129,7 +129,7 @@
     <t>V2</t>
   </si>
   <si>
-    <t>26-07-2026 — FULL REBUILD on CQU/Hyd architecture (this workbook). Adopted quantities (Phase 4), re-sourced rates (Phase 5), FIFO labour x1.08 + crew-days/plant-days/accommodation (Phase 7), markup re-based to directed 41.5% each-on-cost (old effective 45.73% — both shown), GST removed, all external links severed (values frozen from dumps then re-sourced), GT reinstated, WSUD re-based to Reece PC line, kerb chutes carried both ways (D6-F1), basin/spillway $0 allocation-RFI flag. See TCS_CHANGE_LOG.md + MIGRATION_RECONCILIATION.xlsx.</t>
+    <t>26-07-2026 — FULL REBUILD on CQU/Hyd architecture (this workbook). Adopted quantities (Phase 4), re-sourced rates (Phase 5), FIFO labour x1.08 + crew-days/plant-days/accommodation (Phase 7), markup re-based to directed 41.5% each-on-cost (old effective 45.73% — both shown), GST removed, all external links severed (values frozen from dumps then re-sourced), GT reinstated, WSUD re-based to Reece PC line, kerb chutes carried both ways (D6-F1), basin/spillway $0 allocation-RFI flag. LH supervision priced as DIRECT LABOUR per TriCore methodology (correction recorded at change-log S9). See TCS_CHANGE_LOG.md + MIGRATION_RECONCILIATION.xlsx.</t>
   </si>
   <si>
     <t>ASSUMPTIONS &amp; BASIS</t>
@@ -156,7 +156,7 @@
     <t>4.</t>
   </si>
   <si>
-    <t>LH supervision (120 days), establishment non-labour, temp services, EDQ remob, ADAC/CCTV/as-cons are funded from the 5.5% prelims allowance; bottom-up cross-check with variance % on Prelim_OH.</t>
+    <t>Leading Hand supervision (120 days) is DIRECT LABOUR in the Stage 1A/1B labour blocks (row A-14 each), allocated pro-rata to crew-days — per TriCore's existing methodology, which prices TRADESMAN_LEADING HAND as a Day line inside the work-area labour block (old Civ 'SW Zone Sumry' B13/C13/E13 feeding H11; the Hyd master follows the same pattern). It is NOT a preliminary. Establishment non-labour, temp services incl. temp water cartage, EDQ remob and ADAC/CCTV/as-cons are funded from the 5.5% prelims allowance; Prelim_OH builds those bottom-up and carries the variance cross-check (LH row retained there at $0 for traceability).</t>
   </si>
   <si>
     <t>5.</t>
@@ -294,7 +294,7 @@
     <t>Materials (escalated + x1.18 contingency)</t>
   </si>
   <si>
-    <t>Labour (crew-days x FIFO rates)</t>
+    <t>Labour incl. LH supervision (crew-days x FIFO rates)</t>
   </si>
   <si>
     <t>Plant</t>
@@ -351,7 +351,7 @@
     <t>STAGE 1B — 'RECREATIONAL PARK AND PUBLIC AMENITIES' (Sch 3 item 2.3 Drainage)</t>
   </si>
   <si>
-    <t>Labour</t>
+    <t>Labour incl. LH supervision</t>
   </si>
   <si>
     <t>STAGE 1B TOTAL COST</t>
@@ -1077,10 +1077,22 @@
     <t>Trash Box 200 x25 + 150 DWV laterals (grades to 29.2%)</t>
   </si>
   <si>
-    <t>B — LABOUR TOTAL (crew-days / $)</t>
-  </si>
-  <si>
-    <t>LH supervision (120 days) carried in Prelim_OH bottom-up — funded from the 5.5% prelims allowance, not in this cost block.</t>
+    <t>B1 — Crew labour subtotal (crew-days / $)</t>
+  </si>
+  <si>
+    <t>A-14</t>
+  </si>
+  <si>
+    <t>Leading Hand supervision — site-wide (DIRECT LABOUR per TriCore methodology: old Civ 'SW Zone Sumry' B13/C13/E13 prices TRADESMAN_LEADING HAND as a Day line inside the work-area labour block feeding H11; Hyd master follows the same pattern). 120 LH-days allocated pro-rata to crew-days.</t>
+  </si>
+  <si>
+    <t>LH-day</t>
+  </si>
+  <si>
+    <t>B — LABOUR TOTAL (crew labour + LH supervision)</t>
+  </si>
+  <si>
+    <t>LH supervision is DIRECT COST here (not a preliminary) — see TCS_CHANGE_LOG.md S9. Prelim_OH retains a $0 traceability row.</t>
   </si>
   <si>
     <t>C — PLANT (days from Phase 7 roll-up; dry hire unless noted)</t>
@@ -1185,7 +1197,7 @@
     <t>E — ACCOMMODATION &amp; FIFO TRAVEL share (Option A adopted; pro-rata crew-days 1A/(1A+1B))</t>
   </si>
   <si>
-    <t>Accommodation + flights share — Stage 1A</t>
+    <t>Accommodation + flights share — Stage 1A (pro-rata CREW-days, excl. LH supervision days)</t>
   </si>
   <si>
     <t>STAGE 1A — TOTAL COST (materials + labour + plant + subbies + accommodation)</t>
@@ -1254,6 +1266,9 @@
     <t>1B lines 60/61/83 + TB100 x4 + connections</t>
   </si>
   <si>
+    <t>Leading Hand supervision — 1B share (DIRECT LABOUR per TriCore methodology: old Civ 'SW Zone Sumry' B13). 120 LH-days allocated pro-rata to crew-days.</t>
+  </si>
+  <si>
     <t>C — PLANT</t>
   </si>
   <si>
@@ -1269,7 +1284,7 @@
     <t>Spoil haulage &amp; dump</t>
   </si>
   <si>
-    <t>E — ACCOMMODATION &amp; FIFO TRAVEL share (pro-rata crew-days)</t>
+    <t>E — ACCOMMODATION &amp; FIFO TRAVEL share (pro-rata CREW-days, excl. LH supervision days)</t>
   </si>
   <si>
     <t>Accommodation + flights share — Stage 1B</t>
@@ -2388,7 +2403,7 @@
     <t>PRELIMINARIES &amp; OVERHEAD — BOTTOM-UP CROSS-CHECK (TCS)</t>
   </si>
   <si>
-    <t>The sell carries Prelims 5.5% + OH 18% + Profit 18%, EACH calculated ON TOTAL COST per Directive 5.4 (no compounding). This sheet builds prelims bottom-up and cross-checks the 5.5% allowance. Items here are NOT added to the sell — they are funded from the 5.5% pool. All ex GST.</t>
+    <t>The sell carries Prelims 5.5% + OH 18% + Profit 18%, EACH calculated ON TOTAL COST per Directive 5.4 (no compounding). This sheet builds TRUE PRELIMINARIES bottom-up and cross-checks the 5.5% allowance. Items here are NOT added to the sell — they are funded from the 5.5% pool. Leading Hand supervision is NOT a preliminary: per TriCore methodology it is DIRECT LABOUR and is priced in the Stage 1A/1B labour blocks (row retained below at $0 for traceability). All ex GST.</t>
   </si>
   <si>
     <t>Basis / note</t>
@@ -2397,10 +2412,10 @@
     <t>LH SUPERVISION</t>
   </si>
   <si>
-    <t>Leading Hand supervision (site-wide, both stages)</t>
-  </si>
-  <si>
-    <t>Phase 7: LH 120 days x 10 hr; FIFO day rate ex LabourRates_Master (x1.08 uplift).</t>
+    <t>Leading Hand supervision (site-wide, both stages) — REALLOCATED TO DIRECT LABOUR</t>
+  </si>
+  <si>
+    <t>REALLOCATED to direct labour per TriCore methodology (old Civ 'SW Zone Sumry' B13 prices TRADESMAN_LEADING HAND as a Day line inside the work-area labour block) — see TCS_CHANGE_LOG.md S9. Row retained at ZERO for traceability; the 120 LH-days are priced at Stage1A_Drainage A-14 and Stage1B_Drainage A-14. Rate shown for reference.</t>
   </si>
   <si>
     <t>ESTABLISHMENT (non-labour; establishment crew-days are in Stage1A/1B labour A-01/A-12)</t>
@@ -2833,6 +2848,9 @@
   </si>
   <si>
     <t>GT accommodation share (36 cd pro-rata)</t>
+  </si>
+  <si>
+    <t>GT LH supervision share (36 cd pro-rata)</t>
   </si>
   <si>
     <t>GT component cost</t>
@@ -3402,7 +3420,7 @@
       </c>
       <c r="D14" s="24">
         <f>'TCS $ Sched'!D24</f>
-        <v>2547143.5257801986</v>
+        <v>2761814.9756601988</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
@@ -3420,7 +3438,7 @@
       </c>
       <c r="D16" s="24">
         <f>'TCS $ Sched'!D32</f>
-        <v>2658931.2652801988</v>
+        <v>2873602.715160199</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
@@ -3429,7 +3447,7 @@
       </c>
       <c r="D17" s="24">
         <f>'TCS $ Sched'!D44</f>
-        <v>102030.81073167847</v>
+        <v>113131.26256596416</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
@@ -3438,7 +3456,7 @@
       </c>
       <c r="D18" s="24">
         <f>'TCS $ Sched'!D46</f>
-        <v>2760962.076011877</v>
+        <v>2986733.9777261633</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
@@ -3462,7 +3480,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="75" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" ht="87.5" x14ac:dyDescent="0.35">
       <c r="B23" s="14" t="s">
         <v>27</v>
       </c>
@@ -3499,7 +3517,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="25" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" ht="87.5" x14ac:dyDescent="0.35">
       <c r="B29" s="14" t="s">
         <v>36</v>
       </c>
@@ -3656,18 +3674,18 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>130</v>
@@ -3687,22 +3705,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="B6" s="41" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="B7" s="42" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" s="16" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C8" s="18">
         <v>9</v>
@@ -3721,7 +3739,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" s="16" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="C9" s="19">
         <f>55.67*0.18</f>
@@ -3741,13 +3759,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" s="16" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C10" s="18">
         <v>56</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E10" s="28">
         <f>Materials_Master!$H$80</f>
@@ -3760,7 +3778,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="F11" s="9">
         <f>SUM(F8:F10)*Materials_Master!$D$8</f>
@@ -3769,7 +3787,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="C12" s="33">
         <v>9</v>
@@ -3788,13 +3806,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C13" s="33">
         <v>9</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E13" s="28">
         <f>Equip_Master!$D$8</f>
@@ -3807,29 +3825,29 @@
     </row>
     <row r="14" spans="1:7" ht="20" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="F14" s="31">
         <f>(F11+F12+F13)*(1+'TCS $ Sched'!$C$8+'TCS $ Sched'!$C$9+'TCS $ Sched'!$C$10)</f>
         <v>55429.895596924798</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" s="40" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="52" x14ac:dyDescent="0.35">
       <c r="B17" s="41" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="25" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="C18" s="19">
         <f>ROUND(50*1.65*0.125,1)</f>
@@ -3849,13 +3867,13 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C19" s="18">
         <v>12</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="E19" s="28">
         <f>Materials_Master!$H$76</f>
@@ -3868,7 +3886,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="16" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C20" s="18">
         <v>13</v>
@@ -3887,7 +3905,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="F21" s="9">
         <f>SUM(F18:F20)*Materials_Master!$D$8</f>
@@ -3896,7 +3914,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C22" s="33">
         <v>10</v>
@@ -3915,13 +3933,13 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="C23" s="33">
         <v>5</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E23" s="28">
         <f>Equip_Master!$D$8+100</f>
@@ -3934,67 +3952,67 @@
     </row>
     <row r="24" spans="2:7" ht="20" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F24" s="31">
         <f>(F21+F22+F23)*(1+'TCS $ Sched'!$C$8+'TCS $ Sched'!$C$9+'TCS $ Sched'!$C$10)</f>
         <v>52523.570354360883</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="23" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="50" x14ac:dyDescent="0.35">
       <c r="B27" s="16" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="50" x14ac:dyDescent="0.35">
       <c r="B28" s="16" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="25" x14ac:dyDescent="0.35">
       <c r="B29" s="16" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="25" x14ac:dyDescent="0.35">
       <c r="B30" s="16" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="25" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="37.5" x14ac:dyDescent="0.35">
       <c r="B32" s="16" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
     </row>
   </sheetData>
@@ -4004,7 +4022,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
@@ -4017,136 +4035,136 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="160" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="F4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="F5" s="4"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="F6" s="4"/>
       <c r="H6" s="3" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="F7" s="4"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="16" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
       </c>
       <c r="G8" s="12">
-        <f>'TCS $ Sched'!D24-F66</f>
-        <v>2025864.5113955808</v>
+        <f>'TCS $ Sched'!D24-F67</f>
+        <v>2204088.4793844856</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="16" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="F9" s="4"/>
       <c r="H9" s="3" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="16" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -4156,98 +4174,98 @@
         <v>111787.73950000001</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="F11" s="4"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
       </c>
       <c r="G12" s="12">
-        <f>F66</f>
-        <v>521279.0143846178</v>
+        <f>F67</f>
+        <v>557726.49627571332</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="44" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="12">
         <f>'TCS $ Sched'!D24+'TCS $ Sched'!D31</f>
-        <v>2658931.2652801988</v>
+        <v>2873602.715160199</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="F14" s="4"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="16" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>116</v>
@@ -4257,19 +4275,19 @@
         <v>239.11491402180448</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="16" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>116</v>
@@ -4282,14 +4300,14 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="16" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>116</v>
@@ -4302,14 +4320,14 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="16" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>116</v>
@@ -4322,14 +4340,14 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="16" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>116</v>
@@ -4339,126 +4357,126 @@
         <v>390.38510934786962</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="F21" s="4"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="F22" s="4"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="16" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F23" s="4">
         <v>1</v>
       </c>
       <c r="G23" s="12">
         <f>'TCS $ Sched'!D44</f>
-        <v>102030.81073167847</v>
+        <v>113131.26256596416</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="16" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="F24" s="4"/>
       <c r="H24" s="3" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="44" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="12">
         <f>'TCS $ Sched'!D44</f>
-        <v>102030.81073167847</v>
+        <v>113131.26256596416</v>
       </c>
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="F26" s="4"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="16" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>116</v>
@@ -4468,19 +4486,19 @@
         <v>239.11491402180448</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="16" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>116</v>
@@ -4493,14 +4511,14 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="16" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>116</v>
@@ -4513,14 +4531,14 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="16" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>116</v>
@@ -4533,14 +4551,14 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="16" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>116</v>
@@ -4553,12 +4571,12 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B60" s="23" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D61" s="4" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="F61" s="28">
         <f>(Stage1A_Drainage!F54+Stage1A_Drainage!F55+Stage1A_Drainage!F56+Stage1A_Drainage!F57+Stage1A_Drainage!F58)*Materials_Master!$D$8</f>
@@ -4567,7 +4585,7 @@
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D62" s="4" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="F62" s="28">
         <f>Stage1A_Drainage!F101+Stage1A_Drainage!F102</f>
@@ -4576,7 +4594,7 @@
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D63" s="4" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="F63" s="9">
         <f>36*Equip_Master!$D$8+5*Equip_Master!$D$19</f>
@@ -4585,7 +4603,7 @@
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D64" s="4" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="F64" s="9">
         <f>Accommodation!$E$27*36/(Stage1A_Drainage!C103+Stage1B_Drainage!C23)</f>
@@ -4593,21 +4611,30 @@
       </c>
     </row>
     <row r="65" spans="4:6" x14ac:dyDescent="0.35">
-      <c r="D65" s="14" t="s">
-        <v>930</v>
-      </c>
-      <c r="F65" s="12">
-        <f>SUM(F61:F64)</f>
-        <v>368395.06316934124</v>
+      <c r="D65" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="F65" s="9">
+        <f>(Stage1A_Drainage!F104+Stage1B_Drainage!F24)*36/(Stage1A_Drainage!C103+Stage1B_Drainage!C23)</f>
+        <v>25757.937732222934</v>
       </c>
     </row>
     <row r="66" spans="4:6" x14ac:dyDescent="0.35">
-      <c r="D66" s="29" t="s">
-        <v>931</v>
-      </c>
-      <c r="F66" s="30">
-        <f>F65*(1+'TCS $ Sched'!$C$8+'TCS $ Sched'!$C$9+'TCS $ Sched'!$C$10)</f>
-        <v>521279.0143846178</v>
+      <c r="D66" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F66" s="12">
+        <f>SUM(F61:F65)</f>
+        <v>394153.0009015642</v>
+      </c>
+    </row>
+    <row r="67" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D67" s="29" t="s">
+        <v>937</v>
+      </c>
+      <c r="F67" s="30">
+        <f>F66*(1+'TCS $ Sched'!$C$8+'TCS $ Sched'!$C$9+'TCS $ Sched'!$C$10)</f>
+        <v>557726.49627571332</v>
       </c>
     </row>
   </sheetData>
@@ -4711,8 +4738,8 @@
         <v>83</v>
       </c>
       <c r="D16" s="28">
-        <f>Stage1A_Drainage!$F$103</f>
-        <v>606834.33304060157</v>
+        <f>Stage1A_Drainage!$F$105</f>
+        <v>758545.60504060157</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
@@ -4720,7 +4747,7 @@
         <v>84</v>
       </c>
       <c r="D17" s="28">
-        <f>Stage1A_Drainage!$F$121</f>
+        <f>Stage1A_Drainage!$F$123</f>
         <v>165146.73000000001</v>
       </c>
     </row>
@@ -4729,7 +4756,7 @@
         <v>85</v>
       </c>
       <c r="D18" s="28">
-        <f>Stage1A_Drainage!$F$129</f>
+        <f>Stage1A_Drainage!$F$131</f>
         <v>41975</v>
       </c>
     </row>
@@ -4738,7 +4765,7 @@
         <v>86</v>
       </c>
       <c r="D19" s="28">
-        <f>Stage1A_Drainage!$F$132</f>
+        <f>Stage1A_Drainage!$F$134</f>
         <v>105872.41973094171</v>
       </c>
     </row>
@@ -4748,7 +4775,7 @@
       </c>
       <c r="D20" s="30">
         <f>SUM(D15:D19)</f>
-        <v>1800101.4316467838</v>
+        <v>1951812.7036467837</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
@@ -4757,7 +4784,7 @@
       </c>
       <c r="D21" s="9">
         <f>D20*$C$8</f>
-        <v>99005.57874057311</v>
+        <v>107349.69870057311</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
@@ -4766,7 +4793,7 @@
       </c>
       <c r="D22" s="9">
         <f>D20*$C$9</f>
-        <v>324018.25769642106</v>
+        <v>351326.28665642103</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.35">
@@ -4775,7 +4802,7 @@
       </c>
       <c r="D23" s="9">
         <f>D20*$C$10</f>
-        <v>324018.25769642106</v>
+        <v>351326.28665642103</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
@@ -4784,7 +4811,7 @@
       </c>
       <c r="D24" s="31">
         <f>D20+D21+D22+D23</f>
-        <v>2547143.5257801986</v>
+        <v>2761814.9756601988</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.35">
@@ -4846,7 +4873,7 @@
       </c>
       <c r="D32" s="31">
         <f>D24+D31</f>
-        <v>2658931.2652801988</v>
+        <v>2873602.715160199</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.35">
@@ -4868,8 +4895,8 @@
         <v>102</v>
       </c>
       <c r="D36" s="28">
-        <f>Stage1B_Drainage!$F$23</f>
-        <v>31486.68709172932</v>
+        <f>Stage1B_Drainage!$F$25</f>
+        <v>39331.529377443607</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
@@ -4877,7 +4904,7 @@
         <v>84</v>
       </c>
       <c r="D37" s="28">
-        <f>Stage1B_Drainage!$F$29</f>
+        <f>Stage1B_Drainage!$F$31</f>
         <v>2942.12</v>
       </c>
     </row>
@@ -4886,7 +4913,7 @@
         <v>85</v>
       </c>
       <c r="D38" s="28">
-        <f>Stage1B_Drainage!$F$35</f>
+        <f>Stage1B_Drainage!$F$37</f>
         <v>2999.2</v>
       </c>
     </row>
@@ -4895,7 +4922,7 @@
         <v>86</v>
       </c>
       <c r="D39" s="28">
-        <f>Stage1B_Drainage!$F$38</f>
+        <f>Stage1B_Drainage!$F$40</f>
         <v>5493.3802690582961</v>
       </c>
     </row>
@@ -4905,7 +4932,7 @@
       </c>
       <c r="D40" s="30">
         <f>SUM(D35:D39)</f>
-        <v>72106.580022387614</v>
+        <v>79951.422308101886</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.35">
@@ -4914,7 +4941,7 @@
       </c>
       <c r="D41" s="9">
         <f>D40*$C$8</f>
-        <v>3965.8619012313188</v>
+        <v>4397.328226945604</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.35">
@@ -4923,7 +4950,7 @@
       </c>
       <c r="D42" s="9">
         <f>D40*$C$9</f>
-        <v>12979.184404029769</v>
+        <v>14391.256015458339</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
@@ -4932,7 +4959,7 @@
       </c>
       <c r="D43" s="9">
         <f>D40*$C$10</f>
-        <v>12979.184404029769</v>
+        <v>14391.256015458339</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="30" x14ac:dyDescent="0.35">
@@ -4941,7 +4968,7 @@
       </c>
       <c r="D44" s="31">
         <f>D40+D41+D42+D43</f>
-        <v>102030.81073167847</v>
+        <v>113131.26256596416</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>105</v>
@@ -4953,7 +4980,7 @@
       </c>
       <c r="D46" s="32">
         <f>D32+D44</f>
-        <v>2760962.076011877</v>
+        <v>2986733.9777261633</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.35">
@@ -5107,7 +5134,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7315,7 +7342,7 @@
         <v>37211.539290225563</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B103" s="29" t="s">
         <v>344</v>
       </c>
@@ -7327,193 +7354,181 @@
         <f>SUM(F77:F102)</f>
         <v>606834.33304060157</v>
       </c>
-      <c r="G103" s="3" t="s">
+    </row>
+    <row r="104" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A104" s="13" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B105" s="23" t="s">
+      <c r="B104" s="16" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B106" s="16" t="s">
+      <c r="C104" s="19">
+        <f>ROUND(120*C103/(C103+Stage1B_Drainage!$C$23),1)</f>
+        <v>114.1</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C106" s="33">
+      <c r="E104" s="28">
+        <f>LabourRates_Master!$G$11</f>
+        <v>1329.6342857142859</v>
+      </c>
+      <c r="F104" s="9">
+        <f>C104*E104</f>
+        <v>151711.272</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+      <c r="B105" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="F105" s="30">
+        <f>F103+F104</f>
+        <v>758545.60504060157</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B107" s="23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B108" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="C108" s="33">
         <v>43</v>
       </c>
-      <c r="D106" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E106" s="28">
+      <c r="D108" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E108" s="28">
         <f>Equip_Master!$D$5</f>
         <v>317.2</v>
       </c>
-      <c r="F106" s="9">
-        <f t="shared" ref="F106:F120" si="4">C106*E106</f>
+      <c r="F108" s="9">
+        <f t="shared" ref="F108:F122" si="4">C108*E108</f>
         <v>13639.6</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B107" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="C107" s="33">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B109" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C109" s="33">
         <v>64</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E107" s="28">
+      <c r="D109" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E109" s="28">
         <f>Equip_Master!$D$6</f>
         <v>261.17</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F109" s="9">
         <f t="shared" si="4"/>
         <v>16714.88</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B108" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="C108" s="33">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B110" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="C110" s="33">
         <v>66</v>
       </c>
-      <c r="D108" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E108" s="28">
+      <c r="D110" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E110" s="28">
         <f>Equip_Master!$D$7</f>
         <v>314.29000000000002</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F110" s="9">
         <f t="shared" si="4"/>
         <v>20743.140000000003</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B109" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="C109" s="33">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B111" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="C111" s="33">
         <v>56</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E109" s="28">
+      <c r="D111" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E111" s="28">
         <f>Equip_Master!$D$8</f>
         <v>238.67</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F111" s="9">
         <f t="shared" si="4"/>
         <v>13365.519999999999</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="G111" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B112" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="C112" s="33">
+        <v>10</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B110" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="C110" s="33">
-        <v>10</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E110" s="28">
+      <c r="E112" s="28">
         <f>Equip_Master!$D$9</f>
         <v>203</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F112" s="9">
         <f t="shared" si="4"/>
         <v>2030</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B111" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="C111" s="33">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B113" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="C113" s="33">
         <v>60</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E111" s="28">
+      <c r="D113" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E113" s="28">
         <f>Equip_Master!$D$10</f>
         <v>165</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F113" s="9">
         <f t="shared" si="4"/>
         <v>9900</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B112" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="C112" s="33">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B114" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="C114" s="33">
         <v>70</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E112" s="28">
+      <c r="D114" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E114" s="28">
         <f>Equip_Master!$D$11</f>
         <v>34.29</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F114" s="9">
         <f t="shared" si="4"/>
         <v>2400.2999999999997</v>
-      </c>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B113" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="C113" s="33">
-        <v>69</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E113" s="28">
-        <f>Equip_Master!$D$12</f>
-        <v>171.43</v>
-      </c>
-      <c r="F113" s="9">
-        <f t="shared" si="4"/>
-        <v>11828.67</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B114" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="C114" s="33">
-        <v>8</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E114" s="28">
-        <f>Equip_Master!$D$16</f>
-        <v>3800</v>
-      </c>
-      <c r="F114" s="9">
-        <f t="shared" si="4"/>
-        <v>30400</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.35">
@@ -7521,18 +7536,18 @@
         <v>360</v>
       </c>
       <c r="C115" s="33">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E115" s="28">
-        <f>Equip_Master!$D$17</f>
-        <v>2200</v>
+        <f>Equip_Master!$D$12</f>
+        <v>171.43</v>
       </c>
       <c r="F115" s="9">
         <f t="shared" si="4"/>
-        <v>37400</v>
+        <v>11828.67</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>361</v>
@@ -7543,245 +7558,289 @@
         <v>362</v>
       </c>
       <c r="C116" s="33">
+        <v>8</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E116" s="28">
+        <f>Equip_Master!$D$16</f>
+        <v>3800</v>
+      </c>
+      <c r="F116" s="9">
+        <f t="shared" si="4"/>
+        <v>30400</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B117" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="C117" s="33">
+        <v>17</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E117" s="28">
+        <f>Equip_Master!$D$17</f>
+        <v>2200</v>
+      </c>
+      <c r="F117" s="9">
+        <f t="shared" si="4"/>
+        <v>37400</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B118" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="C118" s="33">
         <v>14</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E116" s="28">
+      <c r="D118" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E118" s="28">
         <f>Equip_Master!$D$18</f>
         <v>120</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F118" s="9">
         <f t="shared" si="4"/>
         <v>1680</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B117" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="C117" s="33">
+      <c r="G118" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B119" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="C119" s="33">
         <v>6</v>
       </c>
-      <c r="D117" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E117" s="28">
+      <c r="D119" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E119" s="28">
         <f>Equip_Master!$D$13</f>
         <v>295.77</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F119" s="9">
         <f t="shared" si="4"/>
         <v>1774.62</v>
       </c>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B118" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="C118" s="33">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B120" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C120" s="33">
         <v>2</v>
       </c>
-      <c r="D118" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E118" s="28">
+      <c r="D120" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E120" s="28">
         <f>Equip_Master!$D$15</f>
         <v>1100</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F120" s="9">
         <f t="shared" si="4"/>
         <v>2200</v>
       </c>
-      <c r="G118" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B119" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="C119" s="33">
+      <c r="G120" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B121" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="C121" s="33">
         <v>10</v>
       </c>
-      <c r="D119" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E119" s="28">
+      <c r="D121" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E121" s="28">
         <f>Equip_Master!$D$14</f>
         <v>57</v>
       </c>
-      <c r="F119" s="9">
+      <c r="F121" s="9">
         <f t="shared" si="4"/>
         <v>570</v>
       </c>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B120" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="C120" s="33">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B122" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="C122" s="33">
         <v>5</v>
       </c>
-      <c r="D120" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E120" s="28">
+      <c r="D122" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E122" s="28">
         <f>Equip_Master!$D$19</f>
         <v>100</v>
       </c>
-      <c r="F120" s="9">
+      <c r="F122" s="9">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B121" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="F121" s="30">
-        <f>SUM(F106:F120)</f>
+    <row r="123" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B123" s="29" t="s">
+        <v>372</v>
+      </c>
+      <c r="F123" s="30">
+        <f>SUM(F108:F122)</f>
         <v>165146.73000000001</v>
       </c>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B123" s="23" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B124" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="C124" s="33">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B125" s="23" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B126" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="C126" s="33">
         <v>5</v>
       </c>
-      <c r="D124" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E124" s="28">
+      <c r="D126" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E126" s="28">
         <f>Materials_Master!$H$83</f>
         <v>2070</v>
       </c>
-      <c r="F124" s="9">
-        <f>C124*E124</f>
+      <c r="F126" s="9">
+        <f>C126*E126</f>
         <v>10350</v>
       </c>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B125" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="C125" s="33">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B127" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="C127" s="33">
         <v>1</v>
       </c>
-      <c r="D125" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E125" s="28">
+      <c r="D127" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E127" s="28">
         <f>Materials_Master!$H$84</f>
         <v>1494.9999999999998</v>
       </c>
-      <c r="F125" s="9">
-        <f>C125*E125</f>
-        <v>1494.9999999999998</v>
-      </c>
-    </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B126" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="C126" s="33">
-        <v>40</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="E126" s="28">
-        <f>Materials_Master!$H$85</f>
-        <v>140.29999999999998</v>
-      </c>
-      <c r="F126" s="9">
-        <f>C126*E126</f>
-        <v>5611.9999999999991</v>
-      </c>
-    </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B127" s="16" t="s">
-        <v>374</v>
-      </c>
-      <c r="C127" s="33">
-        <v>4</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="E127" s="28">
-        <f>Materials_Master!$H$86</f>
-        <v>977.49999999999989</v>
-      </c>
       <c r="F127" s="9">
         <f>C127*E127</f>
-        <v>3909.9999999999995</v>
+        <v>1494.9999999999998</v>
       </c>
     </row>
     <row r="128" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B128" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="34">
+      <c r="C128" s="33">
+        <v>40</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E128" s="28">
+        <f>Materials_Master!$H$85</f>
+        <v>140.29999999999998</v>
+      </c>
+      <c r="F128" s="9">
+        <f>C128*E128</f>
+        <v>5611.9999999999991</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B129" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="C129" s="33">
+        <v>4</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="E129" s="28">
+        <f>Materials_Master!$H$86</f>
+        <v>977.49999999999989</v>
+      </c>
+      <c r="F129" s="9">
+        <f>C129*E129</f>
+        <v>3909.9999999999995</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B130" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="C130" s="34">
         <f>ROUND(0.21*(C6+C8+C10+C11+C12+C13+C14+C16+C17+C18)+0.8*130.76,0)</f>
         <v>448</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="D130" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E128" s="28">
+      <c r="E130" s="28">
         <f>Materials_Master!$H$87</f>
         <v>46</v>
       </c>
-      <c r="F128" s="9">
-        <f>C128*E128</f>
+      <c r="F130" s="9">
+        <f>C130*E130</f>
         <v>20608</v>
       </c>
-      <c r="G128" s="13" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="F129" s="30">
-        <f>SUM(F124:F128)</f>
+      <c r="G130" s="13" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B131" s="29" t="s">
+        <v>382</v>
+      </c>
+      <c r="F131" s="30">
+        <f>SUM(F126:F130)</f>
         <v>41975</v>
       </c>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B131" s="23" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F132" s="28">
+    <row r="133" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B133" s="23" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B134" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="F134" s="28">
         <f>Accommodation!$E$27*C103/(C103+Stage1B_Drainage!$C$23)</f>
         <v>105872.41973094171</v>
       </c>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F134" s="31">
-        <f>F74+F103+F121+F129+F132</f>
-        <v>1800101.4316467838</v>
+    <row r="136" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B136" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F136" s="31">
+        <f>F74+F105+F123+F131+F134</f>
+        <v>1951812.7036467837</v>
       </c>
     </row>
   </sheetData>
@@ -7791,7 +7850,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7806,12 +7865,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -7847,7 +7906,7 @@
         <v>135</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C6" s="18">
         <v>29.6</v>
@@ -7870,7 +7929,7 @@
         <v>240</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C7" s="18">
         <v>15.2</v>
@@ -7887,7 +7946,7 @@
         <v>7724.2022399999996</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.35">
@@ -7895,7 +7954,7 @@
         <v>243</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C8" s="18">
         <v>31.4</v>
@@ -7912,7 +7971,7 @@
         <v>12171.525479999997</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -7920,7 +7979,7 @@
         <v>246</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C9" s="18">
         <v>4</v>
@@ -7966,7 +8025,7 @@
         <v>259</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C11" s="19">
         <f>ROUND(0.203*C6,1)</f>
@@ -7990,7 +8049,7 @@
         <v>272</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C12" s="18">
         <v>1</v>
@@ -8013,7 +8072,7 @@
         <v>276</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C13" s="18">
         <v>1</v>
@@ -8042,7 +8101,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" s="14" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F15" s="9">
         <f>F14*(Materials_Master!$D$8-1)</f>
@@ -8060,15 +8119,15 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="23" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C19" s="33">
         <v>2</v>
@@ -8087,10 +8146,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C20" s="33">
         <v>2</v>
@@ -8109,10 +8168,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C21" s="33">
         <v>3</v>
@@ -8131,10 +8190,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C22" s="33">
         <v>4</v>
@@ -8164,170 +8223,202 @@
         <v>31486.68709172932</v>
       </c>
     </row>
+    <row r="24" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C24" s="19">
+        <f>ROUND(120*C23/(Stage1A_Drainage!$C$103+C23),1)</f>
+        <v>5.9</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E24" s="28">
+        <f>LabourRates_Master!$G$11</f>
+        <v>1329.6342857142859</v>
+      </c>
+      <c r="F24" s="9">
+        <f>C24*E24</f>
+        <v>7844.8422857142868</v>
+      </c>
+    </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="23" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B26" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="33">
+      <c r="B25" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="F25" s="30">
+        <f>F23+F24</f>
+        <v>39331.529377443607</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B27" s="23" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B28" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C28" s="33">
         <v>7</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E26" s="28">
+      <c r="D28" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E28" s="28">
         <f>Equip_Master!$D$8</f>
         <v>238.67</v>
       </c>
-      <c r="F26" s="9">
-        <f>C26*E26</f>
+      <c r="F28" s="9">
+        <f>C28*E28</f>
         <v>1670.6899999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C27" s="33">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B29" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C29" s="33">
         <v>1</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E27" s="28">
+      <c r="D29" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E29" s="28">
         <f>Equip_Master!$D$12</f>
         <v>171.43</v>
       </c>
-      <c r="F27" s="9">
-        <f>C27*E27</f>
+      <c r="F29" s="9">
+        <f>C29*E29</f>
         <v>171.43</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C28" s="33">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B30" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="33">
         <v>1</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E28" s="28">
+      <c r="D30" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E30" s="28">
         <f>Equip_Master!$D$15</f>
         <v>1100</v>
       </c>
-      <c r="F28" s="9">
-        <f>C28*E28</f>
+      <c r="F30" s="9">
+        <f>C30*E30</f>
         <v>1100</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="F29" s="30">
-        <f>SUM(F26:F28)</f>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B31" s="29" t="s">
+        <v>372</v>
+      </c>
+      <c r="F31" s="30">
+        <f>SUM(F28:F30)</f>
         <v>2942.12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B31" s="23" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B32" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C32" s="33">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B33" s="23" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B34" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C34" s="33">
         <v>1</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E32" s="28">
+      <c r="D34" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E34" s="28">
         <f>Materials_Master!$H$83</f>
         <v>2070</v>
       </c>
-      <c r="F32" s="9">
-        <f>C32*E32</f>
+      <c r="F34" s="9">
+        <f>C34*E34</f>
         <v>2070</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C33" s="33">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B35" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C35" s="33">
         <v>4</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="E33" s="28">
+      <c r="D35" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E35" s="28">
         <f>Materials_Master!$H$85</f>
         <v>140.29999999999998</v>
       </c>
-      <c r="F33" s="9">
-        <f>C33*E33</f>
+      <c r="F35" s="9">
+        <f>C35*E35</f>
         <v>561.19999999999993</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B34" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="C34" s="34">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B36" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C36" s="34">
         <f>ROUND(0.21*C6+2,0)</f>
         <v>8</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="28">
+      <c r="E36" s="28">
         <f>Materials_Master!$H$87</f>
         <v>46</v>
       </c>
-      <c r="F34" s="9">
-        <f>C34*E34</f>
+      <c r="F36" s="9">
+        <f>C36*E36</f>
         <v>368</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B35" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="F35" s="30">
-        <f>SUM(F32:F34)</f>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B37" s="29" t="s">
+        <v>382</v>
+      </c>
+      <c r="F37" s="30">
+        <f>SUM(F34:F36)</f>
         <v>2999.2</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="23" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B38" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F38" s="28">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B39" s="23" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B40" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="F40" s="28">
         <f>Accommodation!$E$27*C23/(Stage1A_Drainage!$C$103+C23)</f>
         <v>5493.3802690582961</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B40" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F40" s="31">
-        <f>F16+F23+F29+F35+F38</f>
-        <v>72106.580022387614</v>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B42" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F42" s="31">
+        <f>F16+F25+F31+F37+F40</f>
+        <v>79951.422308101886</v>
       </c>
     </row>
   </sheetData>
@@ -8350,22 +8441,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C5" s="5">
         <v>21</v>
@@ -8373,7 +8464,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C6" s="5">
         <v>10</v>
@@ -8381,7 +8472,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C7" s="4">
         <f>C5*C6</f>
@@ -8390,7 +8481,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C8" s="6">
         <v>1.08</v>
@@ -8399,36 +8490,36 @@
     <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D11" s="8">
         <v>25854</v>
@@ -8450,15 +8541,15 @@
         <v>6980.5800000000008</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D12" s="8">
         <v>19764.459298245609</v>
@@ -8480,15 +8571,15 @@
         <v>5336.4040105263148</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D13" s="8">
         <v>16129.36666666667</v>
@@ -8510,15 +8601,15 @@
         <v>4354.929000000001</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F15" s="10">
         <f>2*F12+F13</f>
@@ -8533,12 +8624,12 @@
         <v>15027.737021052631</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="30" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -8563,22 +8654,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4" s="14" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D5" s="15">
         <v>1.38</v>
@@ -8586,7 +8677,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D6" s="15">
         <v>1.1499999999999999</v>
@@ -8594,7 +8685,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D7" s="15">
         <v>1.2</v>
@@ -8602,7 +8693,7 @@
     </row>
     <row r="8" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="B8" s="16" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D8" s="15">
         <v>1.18</v>
@@ -8610,37 +8701,37 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>111</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="17" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>137</v>
@@ -8650,7 +8741,7 @@
         <v>105</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F11" s="18">
         <v>1</v>
@@ -8660,15 +8751,15 @@
         <v>105</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>141</v>
@@ -8677,7 +8768,7 @@
         <v>4.8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F12" s="18">
         <v>1</v>
@@ -8687,15 +8778,15 @@
         <v>4.8</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>137</v>
@@ -8705,7 +8796,7 @@
         <v>183.5655737704918</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F13" s="18">
         <v>1</v>
@@ -8715,15 +8806,15 @@
         <v>183.5655737704918</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>141</v>
@@ -8732,7 +8823,7 @@
         <v>24</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F14" s="18">
         <v>1</v>
@@ -8742,15 +8833,15 @@
         <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>137</v>
@@ -8760,7 +8851,7 @@
         <v>36.076794657762939</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F15" s="19">
         <f t="shared" ref="F15:F29" si="1">$D$5</f>
@@ -8771,15 +8862,15 @@
         <v>49.785976627712849</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>137</v>
@@ -8788,7 +8879,7 @@
         <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F16" s="19">
         <f t="shared" si="1"/>
@@ -8799,15 +8890,15 @@
         <v>82.8</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>137</v>
@@ -8817,7 +8908,7 @@
         <v>92.010118043844855</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F17" s="19">
         <f t="shared" si="1"/>
@@ -8828,15 +8919,15 @@
         <v>126.9739629005059</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>137</v>
@@ -8845,7 +8936,7 @@
         <v>135</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F18" s="19">
         <f t="shared" si="1"/>
@@ -8856,15 +8947,15 @@
         <v>186.29999999999998</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>137</v>
@@ -8874,7 +8965,7 @@
         <v>226.03418803418805</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="F19" s="19">
         <f t="shared" si="1"/>
@@ -8885,15 +8976,15 @@
         <v>311.9271794871795</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>137</v>
@@ -8903,7 +8994,7 @@
         <v>129.41666666666666</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="F20" s="19">
         <f t="shared" si="1"/>
@@ -8914,15 +9005,15 @@
         <v>178.59499999999997</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>137</v>
@@ -8932,7 +9023,7 @@
         <v>36.68333333333333</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F21" s="19">
         <f t="shared" si="1"/>
@@ -8943,15 +9034,15 @@
         <v>50.62299999999999</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>137</v>
@@ -8961,7 +9052,7 @@
         <v>7.1783333333333337</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F22" s="19">
         <f t="shared" si="1"/>
@@ -8972,15 +9063,15 @@
         <v>9.9061000000000003</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>141</v>
@@ -8989,7 +9080,7 @@
         <v>3.5</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F23" s="19">
         <f t="shared" si="1"/>
@@ -9000,15 +9091,15 @@
         <v>4.83</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>141</v>
@@ -9017,7 +9108,7 @@
         <v>3.5</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F24" s="19">
         <f t="shared" si="1"/>
@@ -9028,12 +9119,12 @@
         <v>4.83</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>172</v>
@@ -9045,7 +9136,7 @@
         <v>23.5</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F25" s="19">
         <f t="shared" si="1"/>
@@ -9056,15 +9147,15 @@
         <v>32.43</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>141</v>
@@ -9073,7 +9164,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F26" s="19">
         <f t="shared" si="1"/>
@@ -9084,12 +9175,12 @@
         <v>13.799999999999999</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>176</v>
@@ -9101,7 +9192,7 @@
         <v>60.1</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F27" s="19">
         <f t="shared" si="1"/>
@@ -9112,15 +9203,15 @@
         <v>82.938000000000002</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>141</v>
@@ -9129,7 +9220,7 @@
         <v>38.549999999999997</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F28" s="19">
         <f t="shared" si="1"/>
@@ -9140,15 +9231,15 @@
         <v>53.198999999999991</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>141</v>
@@ -9157,7 +9248,7 @@
         <v>150</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F29" s="19">
         <f t="shared" si="1"/>
@@ -9168,15 +9259,15 @@
         <v>206.99999999999997</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>141</v>
@@ -9185,7 +9276,7 @@
         <v>310</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F30" s="18">
         <v>1</v>
@@ -9195,15 +9286,15 @@
         <v>310</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>141</v>
@@ -9212,7 +9303,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F31" s="18">
         <v>1</v>
@@ -9222,15 +9313,15 @@
         <v>17</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>141</v>
@@ -9239,7 +9330,7 @@
         <v>1095</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="F32" s="18">
         <v>1</v>
@@ -9249,15 +9340,15 @@
         <v>1095</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>141</v>
@@ -9266,7 +9357,7 @@
         <v>1171.2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F33" s="18">
         <v>1</v>
@@ -9276,15 +9367,15 @@
         <v>1171.2</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A34" s="14" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>141</v>
@@ -9293,7 +9384,7 @@
         <v>1404.8</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F34" s="18">
         <v>1</v>
@@ -9303,15 +9394,15 @@
         <v>1404.8</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>141</v>
@@ -9320,7 +9411,7 @@
         <v>1718.4</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F35" s="18">
         <v>1</v>
@@ -9330,15 +9421,15 @@
         <v>1718.4</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>141</v>
@@ -9347,7 +9438,7 @@
         <v>3065.72</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F36" s="18">
         <v>1</v>
@@ -9357,15 +9448,15 @@
         <v>3065.72</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>141</v>
@@ -9374,7 +9465,7 @@
         <v>5891.95</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F37" s="18">
         <v>1</v>
@@ -9384,15 +9475,15 @@
         <v>5891.95</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>141</v>
@@ -9401,7 +9492,7 @@
         <v>317.05</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F38" s="18">
         <v>1</v>
@@ -9411,15 +9502,15 @@
         <v>317.05</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>141</v>
@@ -9428,7 +9519,7 @@
         <v>588.79999999999995</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="F39" s="18">
         <v>1</v>
@@ -9438,15 +9529,15 @@
         <v>588.79999999999995</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A40" s="14" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>141</v>
@@ -9455,7 +9546,7 @@
         <v>158</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="F40" s="18">
         <v>1</v>
@@ -9465,15 +9556,15 @@
         <v>158</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>141</v>
@@ -9482,7 +9573,7 @@
         <v>280</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="F41" s="18">
         <v>1</v>
@@ -9492,15 +9583,15 @@
         <v>280</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A42" s="14" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>141</v>
@@ -9509,7 +9600,7 @@
         <v>352</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="F42" s="18">
         <v>1</v>
@@ -9519,15 +9610,15 @@
         <v>352</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A43" s="14" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>141</v>
@@ -9536,7 +9627,7 @@
         <v>1800.63</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="F43" s="18">
         <v>1</v>
@@ -9546,15 +9637,15 @@
         <v>1800.63</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>141</v>
@@ -9563,7 +9654,7 @@
         <v>2162.6</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F44" s="18">
         <v>1</v>
@@ -9573,15 +9664,15 @@
         <v>2162.6</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>141</v>
@@ -9590,7 +9681,7 @@
         <v>2425.63</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F45" s="18">
         <v>1</v>
@@ -9600,15 +9691,15 @@
         <v>2425.63</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A46" s="14" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>141</v>
@@ -9617,7 +9708,7 @@
         <v>3322.45</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F46" s="18">
         <v>1</v>
@@ -9627,15 +9718,15 @@
         <v>3322.45</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>141</v>
@@ -9644,7 +9735,7 @@
         <v>4222.78</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F47" s="18">
         <v>1</v>
@@ -9654,15 +9745,15 @@
         <v>4222.78</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A48" s="14" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>141</v>
@@ -9671,7 +9762,7 @@
         <v>5241.45</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F48" s="18">
         <v>1</v>
@@ -9681,15 +9772,15 @@
         <v>5241.45</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>141</v>
@@ -9698,7 +9789,7 @@
         <v>1350</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F49" s="18">
         <v>1</v>
@@ -9708,15 +9799,15 @@
         <v>1350</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A50" s="14" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>141</v>
@@ -9725,7 +9816,7 @@
         <v>364</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F50" s="18">
         <v>1</v>
@@ -9735,15 +9826,15 @@
         <v>364</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>141</v>
@@ -9752,7 +9843,7 @@
         <v>400</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F51" s="18">
         <v>1</v>
@@ -9762,15 +9853,15 @@
         <v>400</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A52" s="14" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>141</v>
@@ -9779,7 +9870,7 @@
         <v>1101</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F52" s="18">
         <v>1</v>
@@ -9789,15 +9880,15 @@
         <v>1101</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A53" s="14" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>141</v>
@@ -9806,7 +9897,7 @@
         <v>1403</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F53" s="18">
         <v>1</v>
@@ -9816,15 +9907,15 @@
         <v>1403</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A54" s="14" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>141</v>
@@ -9833,7 +9924,7 @@
         <v>400</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F54" s="18">
         <v>1</v>
@@ -9843,15 +9934,15 @@
         <v>400</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A55" s="14" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>141</v>
@@ -9860,7 +9951,7 @@
         <v>298</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F55" s="18">
         <v>1</v>
@@ -9870,15 +9961,15 @@
         <v>298</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A56" s="14" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>141</v>
@@ -9887,7 +9978,7 @@
         <v>229.5</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F56" s="18">
         <v>1</v>
@@ -9897,15 +9988,15 @@
         <v>229.5</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A57" s="14" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>141</v>
@@ -9914,7 +10005,7 @@
         <v>365.2</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="F57" s="18">
         <v>1</v>
@@ -9924,15 +10015,15 @@
         <v>365.2</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="40" x14ac:dyDescent="0.35">
       <c r="A58" s="14" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>137</v>
@@ -9941,7 +10032,7 @@
         <v>232.94</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F58" s="19">
         <f t="shared" ref="F58:F64" si="3">$D$5</f>
@@ -9952,15 +10043,15 @@
         <v>321.4572</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A59" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>137</v>
@@ -9969,7 +10060,7 @@
         <v>368.24</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F59" s="19">
         <f t="shared" si="3"/>
@@ -9980,15 +10071,15 @@
         <v>508.1712</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A60" s="14" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>137</v>
@@ -9997,7 +10088,7 @@
         <v>280.89</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="F60" s="19">
         <f t="shared" si="3"/>
@@ -10008,15 +10099,15 @@
         <v>387.62819999999994</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="14" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>141</v>
@@ -10025,7 +10116,7 @@
         <v>535.29</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F61" s="19">
         <f t="shared" si="3"/>
@@ -10036,15 +10127,15 @@
         <v>738.70019999999988</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="14" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>141</v>
@@ -10053,7 +10144,7 @@
         <v>214.12</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F62" s="19">
         <f t="shared" si="3"/>
@@ -10064,15 +10155,15 @@
         <v>295.48559999999998</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="14" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>141</v>
@@ -10081,7 +10172,7 @@
         <v>23.53</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F63" s="19">
         <f t="shared" si="3"/>
@@ -10092,15 +10183,15 @@
         <v>32.471399999999996</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="14" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>141</v>
@@ -10109,7 +10200,7 @@
         <v>9.41</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F64" s="19">
         <f t="shared" si="3"/>
@@ -10120,15 +10211,15 @@
         <v>12.985799999999999</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="30" x14ac:dyDescent="0.35">
       <c r="A65" s="14" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>274</v>
@@ -10137,7 +10228,7 @@
         <v>710</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F65" s="19">
         <f t="shared" ref="F65:F71" si="4">$D$7</f>
@@ -10148,15 +10239,15 @@
         <v>852</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="14" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>274</v>
@@ -10165,7 +10256,7 @@
         <v>944.3</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F66" s="19">
         <f t="shared" si="4"/>
@@ -10176,15 +10267,15 @@
         <v>1133.1599999999999</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A67" s="14" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>267</v>
@@ -10193,7 +10284,7 @@
         <v>3750</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="F67" s="19">
         <f t="shared" si="4"/>
@@ -10204,15 +10295,15 @@
         <v>4500</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A68" s="14" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>267</v>
@@ -10221,7 +10312,7 @@
         <v>1250</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="F68" s="19">
         <f t="shared" si="4"/>
@@ -10232,15 +10323,15 @@
         <v>1500</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A69" s="14" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>267</v>
@@ -10249,7 +10340,7 @@
         <v>4750</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F69" s="19">
         <f t="shared" si="4"/>
@@ -10260,15 +10351,15 @@
         <v>5700</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="14" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>267</v>
@@ -10277,7 +10368,7 @@
         <v>2500</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="F70" s="19">
         <f t="shared" si="4"/>
@@ -10288,15 +10379,15 @@
         <v>3000</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A71" s="14" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>267</v>
@@ -10305,7 +10396,7 @@
         <v>500</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="F71" s="19">
         <f t="shared" si="4"/>
@@ -10316,15 +10407,15 @@
         <v>600</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A72" s="14" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>261</v>
@@ -10333,7 +10424,7 @@
         <v>62</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="F72" s="18">
         <v>1</v>
@@ -10343,15 +10434,15 @@
         <v>62</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A73" s="14" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>116</v>
@@ -10360,7 +10451,7 @@
         <v>110</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F73" s="18">
         <v>1</v>
@@ -10370,15 +10461,15 @@
         <v>110</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A74" s="14" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>116</v>
@@ -10387,7 +10478,7 @@
         <v>120</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F74" s="18">
         <v>1</v>
@@ -10397,15 +10488,15 @@
         <v>120</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A75" s="14" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>116</v>
@@ -10414,7 +10505,7 @@
         <v>400</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="F75" s="18">
         <v>1</v>
@@ -10424,24 +10515,24 @@
         <v>400</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="14" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D76" s="8">
         <v>85</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F76" s="18">
         <v>1</v>
@@ -10451,15 +10542,15 @@
         <v>85</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="14" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>261</v>
@@ -10468,7 +10559,7 @@
         <v>48</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="F77" s="18">
         <v>1</v>
@@ -10478,15 +10569,15 @@
         <v>48</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A78" s="14" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>267</v>
@@ -10495,7 +10586,7 @@
         <v>2500</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="F78" s="18">
         <v>1</v>
@@ -10505,15 +10596,15 @@
         <v>2500</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A79" s="14" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>141</v>
@@ -10522,7 +10613,7 @@
         <v>850</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F79" s="18">
         <v>1</v>
@@ -10532,24 +10623,24 @@
         <v>850</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="14" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D80" s="8">
         <v>7</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F80" s="18">
         <v>1</v>
@@ -10559,15 +10650,15 @@
         <v>7</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="14" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>116</v>
@@ -10576,7 +10667,7 @@
         <v>150</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F81" s="18">
         <v>1</v>
@@ -10586,15 +10677,15 @@
         <v>150</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A82" s="14" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>137</v>
@@ -10603,7 +10694,7 @@
         <v>5</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="F82" s="19">
         <f t="shared" ref="F82:F87" si="6">$D$6</f>
@@ -10614,24 +10705,24 @@
         <v>5.75</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="14" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D83" s="8">
         <v>1800</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="F83" s="19">
         <f t="shared" si="6"/>
@@ -10642,24 +10733,24 @@
         <v>2070</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="14" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D84" s="8">
         <v>1300</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="F84" s="19">
         <f t="shared" si="6"/>
@@ -10670,24 +10761,24 @@
         <v>1494.9999999999998</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="14" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D85" s="8">
         <v>122</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="F85" s="19">
         <f t="shared" si="6"/>
@@ -10698,24 +10789,24 @@
         <v>140.29999999999998</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A86" s="14" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D86" s="8">
         <v>850</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="F86" s="19">
         <f t="shared" si="6"/>
@@ -10726,15 +10817,15 @@
         <v>977.49999999999989</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A87" s="14" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>116</v>
@@ -10743,7 +10834,7 @@
         <v>40</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="F87" s="19">
         <f t="shared" si="6"/>
@@ -10754,7 +10845,7 @@
         <v>46</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -10778,30 +10869,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>111</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>114</v>
@@ -10809,321 +10900,321 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D5" s="8">
         <v>317.2</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D6" s="8">
         <v>261.17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D7" s="8">
         <v>314.29000000000002</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D8" s="8">
         <v>238.67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D9" s="8">
         <v>203</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D10" s="8">
         <v>165</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D11" s="8">
         <v>34.29</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D12" s="8">
         <v>171.43</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D13" s="8">
         <v>295.77</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D14" s="8">
         <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D15" s="8">
         <v>1100</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D16" s="8">
         <v>3800</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D17" s="8">
         <v>2200</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D18" s="8">
         <v>120</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="20" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D19" s="8">
         <v>100</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="20" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D20" s="8">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="70" x14ac:dyDescent="0.35">
       <c r="B22" s="21" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -11133,21 +11224,21 @@
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="D24" s="22">
         <v>0</v>
@@ -11164,7 +11255,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B25" s="13" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="D25" s="22">
         <v>300</v>
@@ -11181,7 +11272,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B26" s="13" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="D26" s="22">
         <v>200</v>
@@ -11198,7 +11289,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B27" s="13" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="D27" s="22">
         <v>250</v>
@@ -11215,7 +11306,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B28" s="13" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="D28" s="22">
         <v>310</v>
@@ -11232,7 +11323,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D29" s="22">
         <v>440</v>
@@ -11249,7 +11340,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="D30" s="22">
         <v>450</v>
@@ -11266,7 +11357,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B31" s="13" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="D31" s="22">
         <v>26</v>
@@ -11283,7 +11374,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B32" s="13" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="D32" s="22">
         <v>26</v>
@@ -11300,7 +11391,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D33" s="22">
         <v>30</v>
@@ -11317,7 +11408,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="13" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="D34" s="22">
         <v>115</v>
@@ -11334,7 +11425,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="13" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="D35" s="22">
         <v>50</v>
@@ -11351,7 +11442,7 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B36" s="13" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="D36" s="22">
         <v>180</v>
@@ -11368,7 +11459,7 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B37" s="13" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="D37" s="22">
         <v>400</v>
@@ -11385,7 +11476,7 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="13" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D38" s="22">
         <v>341</v>
@@ -11402,7 +11493,7 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="13" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="D39" s="22">
         <v>50</v>
@@ -11419,7 +11510,7 @@
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="13" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="D40" s="22">
         <v>180</v>
@@ -11436,7 +11527,7 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="13" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="D41" s="22">
         <v>150</v>
@@ -11453,7 +11544,7 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="13" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="D42" s="22">
         <v>150</v>
@@ -11470,7 +11561,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="13" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="D43" s="22">
         <v>5</v>
@@ -11487,7 +11578,7 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="13" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="D44" s="22">
         <v>0</v>
@@ -11504,7 +11595,7 @@
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="13" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="D45" s="22">
         <v>5</v>
@@ -11521,7 +11612,7 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="13" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="D46" s="22">
         <v>0</v>
@@ -11538,7 +11629,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="13" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="D47" s="22">
         <v>50</v>
@@ -11555,7 +11646,7 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="13" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D48" s="22">
         <v>0</v>
@@ -11572,7 +11663,7 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="13" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D49" s="22">
         <v>0</v>
@@ -11589,7 +11680,7 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B50" s="13" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D50" s="22">
         <v>0</v>
@@ -11606,7 +11697,7 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B51" s="13" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D51" s="22">
         <v>0</v>
@@ -11623,7 +11714,7 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B52" s="13" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D52" s="22">
         <v>0</v>
@@ -11640,7 +11731,7 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B53" s="13" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="D53" s="22">
         <v>0</v>
@@ -11657,7 +11748,7 @@
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B54" s="13" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D54" s="22">
         <v>25</v>
@@ -11674,7 +11765,7 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B55" s="13" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="D55" s="22">
         <v>125</v>
@@ -11691,7 +11782,7 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B56" s="13" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="D56" s="22">
         <v>40</v>
@@ -11708,7 +11799,7 @@
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B57" s="13" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="D57" s="22">
         <v>200</v>
@@ -11725,7 +11816,7 @@
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B58" s="13" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D58" s="22">
         <v>0</v>
@@ -11759,39 +11850,39 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="C4" s="8">
         <v>4606.0600000000004</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="C5" s="39">
         <v>103.24679999999999</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C6" s="5">
         <v>25</v>
@@ -11799,18 +11890,18 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="C7" s="8">
         <v>200</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C8" s="5">
         <v>2</v>
@@ -11819,27 +11910,27 @@
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C11" s="5">
         <v>10</v>
@@ -11863,7 +11954,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="C12" s="5">
         <v>10</v>
@@ -11887,7 +11978,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="C13" s="5">
         <v>7</v>
@@ -11911,7 +12002,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C14" s="5">
         <v>4</v>
@@ -11935,7 +12026,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C15" s="5">
         <v>7</v>
@@ -11959,7 +12050,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="C16" s="5">
         <v>7</v>
@@ -11983,7 +12074,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="29" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="C17" s="14">
         <f>SUM(C11:C16)</f>
@@ -12008,7 +12099,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C19" s="4">
         <f>6*$C$6</f>
@@ -12021,7 +12112,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="E21" s="31">
         <f>E17+E19</f>
@@ -12030,7 +12121,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="E22" s="9">
         <f>G17</f>
@@ -12039,7 +12130,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="13" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="E23" s="9">
         <f>E22-E21</f>
@@ -12048,7 +12139,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="E25" s="9">
         <f>C17*$C$8*2*$C$7</f>
@@ -12057,7 +12148,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="E27" s="30">
         <f>E21+E25</f>
@@ -12084,18 +12175,18 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>130</v>
@@ -12110,23 +12201,23 @@
         <v>132</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="23" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="50" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C6" s="33">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E6" s="28">
         <f>LabourRates_Master!$G$11</f>
@@ -12134,20 +12225,20 @@
       </c>
       <c r="F6" s="9">
         <f>C6*E6</f>
-        <v>159556.11428571431</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" s="23" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" s="16" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C8" s="33">
         <v>1</v>
@@ -12163,18 +12254,18 @@
         <v>4500</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" s="16" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C9" s="33">
         <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E9" s="8">
         <v>150</v>
@@ -12184,18 +12275,18 @@
         <v>900</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" s="16" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C10" s="33">
         <v>6</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E10" s="8">
         <v>1600</v>
@@ -12205,18 +12296,18 @@
         <v>9600</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" s="16" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C11" s="33">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E11" s="8">
         <v>400</v>
@@ -12226,18 +12317,18 @@
         <v>2400</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="16" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C12" s="33">
         <v>6</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E12" s="8">
         <v>180</v>
@@ -12247,18 +12338,18 @@
         <v>1080</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" s="16" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="C13" s="33">
         <v>6</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E13" s="8">
         <v>400</v>
@@ -12268,18 +12359,18 @@
         <v>2400</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="C14" s="33">
         <v>6</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E14" s="8">
         <v>541</v>
@@ -12289,18 +12380,18 @@
         <v>3246</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" s="16" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C15" s="33">
         <v>6</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E15" s="8">
         <v>600</v>
@@ -12310,23 +12401,23 @@
         <v>3600</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" s="23" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="16" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C17" s="33">
         <v>26</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="E17" s="8">
         <v>120</v>
@@ -12336,18 +12427,18 @@
         <v>3120</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="C18" s="33">
         <v>26</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="E18" s="8">
         <v>130</v>
@@ -12357,12 +12448,12 @@
         <v>3380</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C19" s="33">
         <v>1</v>
@@ -12378,18 +12469,18 @@
         <v>6000</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="16" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="C20" s="33">
         <v>26</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="E20" s="8">
         <v>25</v>
@@ -12399,17 +12490,17 @@
         <v>650</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="23" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="20" x14ac:dyDescent="0.35">
       <c r="B22" s="16" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C22" s="33">
         <v>2</v>
@@ -12425,17 +12516,17 @@
         <v>1600</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="23" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="25" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="C24" s="34">
         <f>ROUND(Stage1A_Drainage!C6+Stage1A_Drainage!C8+Stage1A_Drainage!C10+Stage1A_Drainage!C11+Stage1A_Drainage!C12+Stage1A_Drainage!C13+Stage1A_Drainage!C14+Stage1A_Drainage!C16+Stage1A_Drainage!C17+Stage1A_Drainage!C18+Stage1B_Drainage!C6,0)</f>
@@ -12453,12 +12544,12 @@
         <v>9585.25</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="16" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C25" s="33">
         <v>1</v>
@@ -12474,12 +12565,12 @@
         <v>4500</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="C26" s="33">
         <v>1</v>
@@ -12495,12 +12586,12 @@
         <v>3500</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B27" s="16" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="C27" s="33">
         <v>1</v>
@@ -12516,68 +12607,68 @@
         <v>2500</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="29" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="F29" s="30">
         <f>SUM(F5:F27)</f>
-        <v>222117.36428571431</v>
+        <v>62561.25</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="14" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="F31" s="12">
-        <f>0.055*(Stage1A_Drainage!$F$134+Stage1B_Drainage!$F$40)</f>
-        <v>102971.44064180444</v>
+        <f>0.055*(Stage1A_Drainage!$F$136+Stage1B_Drainage!$F$42)</f>
+        <v>111747.0269275187</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B32" s="2" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="F32" s="31">
         <f>F31-F29</f>
-        <v>-119145.92364390987</v>
+        <v>49185.776927518702</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="14" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="F33" s="27">
         <f>F29/F31-1</f>
-        <v>1.1570773692325997</v>
+        <v>-0.44015289068425556</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B35" s="23" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="F36" s="9">
-        <f>0.18*(Stage1A_Drainage!$F$134+Stage1B_Drainage!$F$40)</f>
-        <v>336997.44210045086</v>
+        <f>0.18*(Stage1A_Drainage!$F$136+Stage1B_Drainage!$F$42)</f>
+        <v>365717.5426718794</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C37" s="5">
         <v>6</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E37" s="8">
         <v>20000</v>
@@ -12589,11 +12680,11 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="13" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="F38" s="9">
         <f>F36-F37</f>
-        <v>216997.44210045086</v>
+        <v>245717.5426718794</v>
       </c>
     </row>
   </sheetData>

--- a/Working_Cost_Models/TCS/ROK_TCS_CostModel_V2.xlsx
+++ b/Working_Cost_Models/TCS/ROK_TCS_CostModel_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tricoreplumbing-my.sharepoint.com/personal/mitch_tricoreplumbing_com_au/Documents/Documents/GitHub/ROK Sports Precinct - Stage 1/Working_Cost_Models/TCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_ADC74B1B7F38351349CD6DE73C5C97F7A66738FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_ADC74B1B7F38351349CD6DE73C5C97F7A66738FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2113C139-092D-4F3E-B413-0AC12718C1C8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover_Control" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="948">
   <si>
     <t>ROK SPORTS PRECINCT — STAGE 1  |  TCS COST MODEL V2</t>
   </si>
@@ -2523,9 +2523,6 @@
     <t>RPEQ certification + as-constructed drawing preparation</t>
   </si>
   <si>
-    <t>Estimator allowance; surveyor pickup attendance already in Stage subbies.</t>
-  </si>
-  <si>
     <t>Drainage clean / pre-PC de-silt (S24)</t>
   </si>
   <si>
@@ -2616,9 +2613,6 @@
     <t>SPILLWAY ADD-PRICE IF ALLOCATED TO TCS (cost x 1.415)</t>
   </si>
   <si>
-    <t>Reinstatement: set Stage1A_Drainage labour B-07 = 10 cd; enter spillway material rows at X1; add 5 plant-days 3-5T.</t>
-  </si>
-  <si>
     <t>E3 — RECORDS (excluded / relocated items — nothing lost silently)</t>
   </si>
   <si>
@@ -2857,18 +2851,55 @@
   </si>
   <si>
     <t>GT component SELL (x 1.415 on cost)</t>
+  </si>
+  <si>
+    <t>EXCLUDED per Director decision 27 Jul 2026. Rate retained at E26 for reference; quantity zeroed so the audit trail survives (same convention as the LH row B6). CONSEQUENCE FOR DIRECTOR: this line bundled as-constructed DRAWING PREPARATION with RPEQ certification - removing $3,500 removes both. ADAC XML preparation + validation remains separately priced at Prelim_OH!B25 ($4,500) and as-constructed survey / ADAC attendance labour remains at Stage1A_Drainage A-10 and Stage1B_Drainage A-13, so as-constructeds are PARTIALLY but not WHOLLY covered. No compensating adjustment made.</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Concrete surround to grated trench channels GT1-GT4 + GT7-GT9 (F1320 typical trench details)</t>
+  </si>
+  <si>
+    <t>SOURCE: VOL 15 SE_12306_F1320-T1 'HAURATON RECYFIX PRO 200 TYPE 10 / TYPE 010 TRENCH' and 'PRO 100 TYPE 010 TRENCH' typical details - dimensioned CONCRETE SURROUND. PRO200: 500 wide (119+262+119) x 350 deep (200 channel + 150 under channel) less 262x200 channel body = 0.1226 m3/m. PRO100: 450 wide (145+160+145) x 350 deep less 160x200 = 0.1255 m3/m. Qty = G1 (548.8 m PRO200) x 0.1226 + G2 (13.1 m PRO100) x 0.1255. Rate = Materials_Master M65 H75 ($400/m3, 'Concrete 32 MPa (spillway/surrounds)'). Closes the gap where EBC E3 and 01_SCOPE_MATRIX.md L1 both claimed excavation AND quarry were reinstated while Q1's bedding formula (C62) structurally excluded every GT row. Install labour already carried at C-06.</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>Crushed rock base to grated trench channels GT1-GT4 + GT7-GT9 (F1320 typical trench details)</t>
+  </si>
+  <si>
+    <t>SOURCE: same F1320 details - dimensioned 'CRUSHED ROCK BASE' 100 thick extending 150 beyond the concrete each side. PRO200: 0.800 x 0.100 = 0.080 m3/m. PRO100: 0.750 x 0.100 = 0.075 m3/m. Converted to tonnes at 2.10 T/m3 - the model's OWN implied Type 2.3 density (EBC C20 = 13 T against the EBC C18 spillway geometry 82.5 m2 x 0.075 m = 6.19 m3). Rate = Materials_Master M67 H77 ($48/T, Type 2.3 sub-base, ex old Civ CBR15 rate). NOT priced on the pipe-trench 0.203 T/m factor: the drawing gives a dimensioned section, so the measured detail governs (Rule 2).</t>
+  </si>
+  <si>
+    <t>Concrete surround to grated trench channels GT5 + GT6 (F1320 typical trench details)</t>
+  </si>
+  <si>
+    <t>SOURCE: VOL 15 SE_12306_F1320-T1 Hauraton typical trench details. PRO200 0.1226 m3/m x G2 GT6 31.4 m; PRO100 0.1255 m3/m x G1 GT5 15.2 m. Concrete surround 500/450 wide x 350 deep less channel body. Rate Materials_Master M65 H75. See Stage1A_Drainage G64 for the full derivation.</t>
+  </si>
+  <si>
+    <t>Crushed rock base to grated trench channels GT5 + GT6 (F1320 typical trench details)</t>
+  </si>
+  <si>
+    <t>SOURCE: same F1320 details - crushed rock base 100 thick x (concrete width + 150 each side). 0.080 m3/m PRO200 / 0.075 m3/m PRO100, converted at 2.10 T/m3 (model's own Type 2.3 density, EBC C20/C18). Rate Materials_Master M67 H77. See Stage1A_Drainage G65.</t>
+  </si>
+  <si>
+    <t>EXCLUDED externally per Director decision 27 Jul 2026; add-price retained for reinstatement; client-facing exclusion sentence required (closes UC-07). Director's test applied: not pipe, not pit, not a scour pad off a headwall - fails all three limbs. VERIFIED sub-component by sub-component against F1323/F1305: B18 spillway concrete 25 MPa, B19 SL72 mesh, B20 Type 2.3 sub-base, B22 labour B-07, B23 plant - no pipe, pit or scour-pad element is bundled in this build-up. The basin's rock pads (D50=500 x 900 deep, C10 inlet/outlet) and the C10 RCBC 2700x1200 outlet and its BCC headwalls are SEPARATE and already in base at Stage1A_Drainage R3, C6 and H11 - nothing is double-carried. Base remains $0: Stage1A_Drainage X1 = 0 and labour B-07 = 0 crew-days (both confirmed 27 Jul 2026). Reinstatement instructions above remain valid if the Director reverses.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="\$#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -2965,7 +2996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3029,6 +3060,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3332,7 +3364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:D45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -3340,12 +3372,12 @@
     <col min="4" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>1</v>
       </c>
@@ -3353,7 +3385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
@@ -3361,7 +3393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="25" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B6" s="14" t="s">
         <v>5</v>
       </c>
@@ -3369,7 +3401,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
@@ -3377,7 +3409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
         <v>9</v>
       </c>
@@ -3385,7 +3417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="14" t="s">
         <v>11</v>
       </c>
@@ -3393,7 +3425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
         <v>13</v>
       </c>
@@ -3401,7 +3433,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="25" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
@@ -3409,21 +3441,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="24">
         <f>'TCS $ Sched'!D24</f>
-        <v>2761814.9756601988</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+        <v>2815365.5940601984</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="s">
         <v>19</v>
       </c>
@@ -3432,34 +3464,34 @@
         <v>111787.73950000001</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="24">
         <f>'TCS $ Sched'!D32</f>
-        <v>2873602.715160199</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+        <v>2927153.3335601985</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="24">
         <f>'TCS $ Sched'!D44</f>
-        <v>113131.26256596416</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+        <v>117646.13136596419</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="14" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="24">
         <f>'TCS $ Sched'!D46</f>
-        <v>2986733.9777261633</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+        <v>3044799.4649261627</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
         <v>23</v>
       </c>
@@ -3467,12 +3499,12 @@
         <v>890849.95</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="50" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" ht="52.8" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
         <v>25</v>
       </c>
@@ -3480,7 +3512,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" ht="92.4" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>27</v>
       </c>
@@ -3488,12 +3520,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="25" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B26" s="14" t="s">
         <v>30</v>
       </c>
@@ -3501,7 +3533,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" ht="39.6" x14ac:dyDescent="0.3">
       <c r="B27" s="14" t="s">
         <v>32</v>
       </c>
@@ -3509,7 +3541,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:4" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" ht="39.6" x14ac:dyDescent="0.3">
       <c r="B28" s="14" t="s">
         <v>34</v>
       </c>
@@ -3517,7 +3549,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" ht="92.4" x14ac:dyDescent="0.3">
       <c r="B29" s="14" t="s">
         <v>36</v>
       </c>
@@ -3525,7 +3557,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="2:4" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" ht="39.6" x14ac:dyDescent="0.3">
       <c r="B30" s="14" t="s">
         <v>38</v>
       </c>
@@ -3533,7 +3565,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="25" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B31" s="14" t="s">
         <v>40</v>
       </c>
@@ -3541,7 +3573,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="2:4" ht="50" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" ht="52.8" x14ac:dyDescent="0.3">
       <c r="B32" s="14" t="s">
         <v>42</v>
       </c>
@@ -3549,7 +3581,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="50" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
         <v>44</v>
       </c>
@@ -3557,7 +3589,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B34" s="14" t="s">
         <v>46</v>
       </c>
@@ -3565,7 +3597,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
         <v>48</v>
       </c>
@@ -3573,7 +3605,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
         <v>50</v>
       </c>
@@ -3581,7 +3613,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B37" s="14" t="s">
         <v>52</v>
       </c>
@@ -3589,7 +3621,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B38" s="14" t="s">
         <v>54</v>
       </c>
@@ -3597,7 +3629,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B39" s="14" t="s">
         <v>56</v>
       </c>
@@ -3605,7 +3637,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B40" s="14" t="s">
         <v>58</v>
       </c>
@@ -3613,7 +3645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B41" s="14" t="s">
         <v>60</v>
       </c>
@@ -3621,7 +3653,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B42" s="14" t="s">
         <v>62</v>
       </c>
@@ -3629,7 +3661,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B43" s="14" t="s">
         <v>64</v>
       </c>
@@ -3637,7 +3669,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B44" s="14" t="s">
         <v>66</v>
       </c>
@@ -3645,7 +3677,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="25" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B45" s="14" t="s">
         <v>68</v>
       </c>
@@ -3661,7 +3693,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -3672,17 +3704,17 @@
     <col min="7" max="7" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
         <v>450</v>
@@ -3703,24 +3735,24 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="40" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B6" s="41" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.35">
-      <c r="B6" s="41" t="s">
+    <row r="7" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="42" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.35">
-      <c r="B7" s="42" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
         <v>841</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B8" s="16" t="s">
-        <v>842</v>
       </c>
       <c r="C8" s="18">
         <v>9</v>
@@ -3737,9 +3769,9 @@
         <v>7650</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C9" s="19">
         <f>55.67*0.18</f>
@@ -3757,7 +3789,7 @@
         <v>1503.09</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
         <v>664</v>
       </c>
@@ -3776,18 +3808,18 @@
         <v>392</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F11" s="9">
         <f>SUM(F8:F10)*Materials_Master!$D$8</f>
         <v>11263.206199999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C12" s="33">
         <v>9</v>
@@ -3804,9 +3836,9 @@
         <v>25761.834893233081</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C13" s="33">
         <v>9</v>
@@ -3823,31 +3855,31 @@
         <v>2148.0299999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F14" s="31">
         <f>(F11+F12+F13)*(1+'TCS $ Sched'!$C$8+'TCS $ Sched'!$C$9+'TCS $ Sched'!$C$10)</f>
         <v>55429.895596924798</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="40" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B16" s="40" t="s">
+    <row r="17" spans="2:7" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="41" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="52" x14ac:dyDescent="0.35">
-      <c r="B17" s="41" t="s">
+    <row r="18" spans="2:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B18" s="16" t="s">
         <v>850</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="B18" s="16" t="s">
-        <v>851</v>
       </c>
       <c r="C18" s="19">
         <f>ROUND(50*1.65*0.125,1)</f>
@@ -3865,9 +3897,9 @@
         <v>4120</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="16" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C19" s="18">
         <v>12</v>
@@ -3884,9 +3916,9 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="16" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C20" s="18">
         <v>13</v>
@@ -3903,18 +3935,18 @@
         <v>624</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F21" s="9">
         <f>SUM(F18:F20)*Materials_Master!$D$8</f>
         <v>6801.5199999999995</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C22" s="33">
         <v>10</v>
@@ -3931,9 +3963,9 @@
         <v>28624.260992481199</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C23" s="33">
         <v>5</v>
@@ -3950,69 +3982,69 @@
         <v>1693.35</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="91.8" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F24" s="31">
         <f>(F21+F22+F23)*(1+'TCS $ Sched'!$C$8+'TCS $ Sched'!$C$9+'TCS $ Sched'!$C$10)</f>
         <v>52523.570354360883</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="23" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="16" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="23" t="s">
+      <c r="F27" s="14" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="50" x14ac:dyDescent="0.35">
-      <c r="B27" s="16" t="s">
+    <row r="28" spans="2:7" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="B28" s="16" t="s">
         <v>859</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F28" s="14" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="50" x14ac:dyDescent="0.35">
-      <c r="B28" s="16" t="s">
+    <row r="29" spans="2:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B29" s="16" t="s">
         <v>861</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F29" s="14" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="B29" s="16" t="s">
+    <row r="30" spans="2:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B30" s="16" t="s">
         <v>863</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F30" s="14" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B31" s="16" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="30" spans="2:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="B30" s="16" t="s">
+      <c r="F31" s="14" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B32" s="16" t="s">
         <v>865</v>
       </c>
-      <c r="F30" s="14" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="B31" s="16" t="s">
+      <c r="F32" s="14" t="s">
         <v>866</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="16" t="s">
-        <v>867</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>868</v>
       </c>
     </row>
   </sheetData>
@@ -4023,7 +4055,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="64" customWidth="1"/>
@@ -4033,94 +4065,94 @@
     <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="163.19999999999999" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="160" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+      <c r="B4" s="13" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="20" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>871</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="43" t="s">
         <v>872</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>873</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>874</v>
       </c>
       <c r="F4" s="4"/>
       <c r="H4" s="3" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>874</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>871</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="D5" s="43" t="s">
         <v>876</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>877</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>878</v>
       </c>
       <c r="F5" s="4"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>877</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>879</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>880</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>881</v>
       </c>
       <c r="F6" s="4"/>
       <c r="H6" s="3" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>881</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>871</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="D7" s="43" t="s">
         <v>883</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>884</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>885</v>
       </c>
       <c r="F7" s="4"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="16" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>450</v>
@@ -4130,38 +4162,38 @@
       </c>
       <c r="G8" s="12">
         <f>'TCS $ Sched'!D24-F67</f>
-        <v>2204088.4793844856</v>
+        <v>2257639.0977844852</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.35">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="16" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="F9" s="4"/>
       <c r="H9" s="3" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.35">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="16" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>450</v>
@@ -4174,37 +4206,37 @@
         <v>111787.73950000001</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>893</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
-        <v>871</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="D11" s="43" t="s">
         <v>895</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>896</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>897</v>
       </c>
       <c r="F11" s="4"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>898</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>899</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>900</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>450</v>
@@ -4217,55 +4249,55 @@
         <v>557726.49627571332</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="44" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="12">
         <f>'TCS $ Sched'!D24+'TCS $ Sched'!D31</f>
-        <v>2873602.715160199</v>
+        <v>2927153.3335601985</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>903</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="13" t="s">
-        <v>871</v>
-      </c>
-      <c r="B14" s="13" t="s">
+      <c r="D14" s="43" t="s">
         <v>905</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>906</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>907</v>
       </c>
       <c r="F14" s="4"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="16" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>116</v>
@@ -4275,19 +4307,19 @@
         <v>239.11491402180448</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="16" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>116</v>
@@ -4298,16 +4330,16 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="16" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>116</v>
@@ -4318,16 +4350,16 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>116</v>
@@ -4338,16 +4370,16 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="16" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>116</v>
@@ -4357,51 +4389,51 @@
         <v>390.38510934786962</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>874</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>875</v>
+      </c>
+      <c r="D21" s="43" t="s">
         <v>876</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>877</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>878</v>
       </c>
       <c r="F21" s="4"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="F22" s="4"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
+        <v>915</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>917</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>919</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="16" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>450</v>
@@ -4411,72 +4443,72 @@
       </c>
       <c r="G23" s="12">
         <f>'TCS $ Sched'!D44</f>
-        <v>113131.26256596416</v>
+        <v>117646.13136596419</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="20" x14ac:dyDescent="0.35">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="16" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="F24" s="4"/>
       <c r="H24" s="3" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="44" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="12">
         <f>'TCS $ Sched'!D44</f>
-        <v>113131.26256596416</v>
+        <v>117646.13136596419</v>
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="F26" s="4"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="16" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>116</v>
@@ -4486,19 +4518,19 @@
         <v>239.11491402180448</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="16" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>116</v>
@@ -4509,16 +4541,16 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="16" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>116</v>
@@ -4529,16 +4561,16 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>116</v>
@@ -4549,16 +4581,16 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="16" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>116</v>
@@ -4569,68 +4601,68 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="23" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.35">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D61" s="4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="F61" s="28">
         <f>(Stage1A_Drainage!F54+Stage1A_Drainage!F55+Stage1A_Drainage!F56+Stage1A_Drainage!F57+Stage1A_Drainage!F58)*Materials_Master!$D$8</f>
         <v>238277.26817039997</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D62" s="4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="F62" s="28">
-        <f>Stage1A_Drainage!F101+Stage1A_Drainage!F102</f>
+        <f>Stage1A_Drainage!F103+Stage1A_Drainage!F104</f>
         <v>103047.33957293231</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D63" s="4" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F63" s="9">
         <f>36*Equip_Master!$D$8+5*Equip_Master!$D$19</f>
         <v>9092.119999999999</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D64" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="F64" s="9">
+        <f>Accommodation!$E$27*36/(Stage1A_Drainage!C105+Stage1B_Drainage!C25)</f>
+        <v>17978.335426008969</v>
+      </c>
+    </row>
+    <row r="65" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D65" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="F65" s="9">
+        <f>(Stage1A_Drainage!F106+Stage1B_Drainage!F26)*36/(Stage1A_Drainage!C105+Stage1B_Drainage!C25)</f>
+        <v>25757.937732222934</v>
+      </c>
+    </row>
+    <row r="66" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D66" s="14" t="s">
         <v>934</v>
-      </c>
-      <c r="F64" s="9">
-        <f>Accommodation!$E$27*36/(Stage1A_Drainage!C103+Stage1B_Drainage!C23)</f>
-        <v>17978.335426008969</v>
-      </c>
-    </row>
-    <row r="65" spans="4:6" x14ac:dyDescent="0.35">
-      <c r="D65" s="4" t="s">
-        <v>935</v>
-      </c>
-      <c r="F65" s="9">
-        <f>(Stage1A_Drainage!F104+Stage1B_Drainage!F24)*36/(Stage1A_Drainage!C103+Stage1B_Drainage!C23)</f>
-        <v>25757.937732222934</v>
-      </c>
-    </row>
-    <row r="66" spans="4:6" x14ac:dyDescent="0.35">
-      <c r="D66" s="14" t="s">
-        <v>936</v>
       </c>
       <c r="F66" s="12">
         <f>SUM(F61:F65)</f>
         <v>394153.0009015642</v>
       </c>
     </row>
-    <row r="67" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D67" s="29" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="F67" s="30">
         <f>F66*(1+'TCS $ Sched'!$C$8+'TCS $ Sched'!$C$9+'TCS $ Sched'!$C$10)</f>
@@ -4645,7 +4677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H56"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="64" customWidth="1"/>
@@ -4653,37 +4685,37 @@
     <col min="8" max="8" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="30" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="30.6" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>76</v>
       </c>
@@ -4694,7 +4726,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>78</v>
       </c>
@@ -4702,7 +4734,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>79</v>
       </c>
@@ -4710,7 +4742,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>80</v>
       </c>
@@ -4719,107 +4751,107 @@
         <v>0.41499999999999998</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>82</v>
       </c>
       <c r="D15" s="28">
-        <f>Stage1A_Drainage!$F$74</f>
-        <v>880272.94887524052</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+        <f>Stage1A_Drainage!$F$76</f>
+        <v>918117.90887524048</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>83</v>
       </c>
       <c r="D16" s="28">
-        <f>Stage1A_Drainage!$F$105</f>
+        <f>Stage1A_Drainage!$F$107</f>
         <v>758545.60504060157</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="28">
-        <f>Stage1A_Drainage!$F$123</f>
+        <f>Stage1A_Drainage!$F$125</f>
         <v>165146.73000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>85</v>
       </c>
       <c r="D18" s="28">
-        <f>Stage1A_Drainage!$F$131</f>
+        <f>Stage1A_Drainage!$F$133</f>
         <v>41975</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D19" s="28">
-        <f>Stage1A_Drainage!$F$134</f>
+        <f>Stage1A_Drainage!$F$136</f>
         <v>105872.41973094171</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="29" t="s">
         <v>87</v>
       </c>
       <c r="D20" s="30">
         <f>SUM(D15:D19)</f>
-        <v>1951812.7036467837</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+        <v>1989657.6636467837</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>88</v>
       </c>
       <c r="D21" s="9">
         <f>D20*$C$8</f>
-        <v>107349.69870057311</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+        <v>109431.17150057311</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="9">
         <f>D20*$C$9</f>
-        <v>351326.28665642103</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+        <v>358138.37945642107</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D23" s="9">
         <f>D20*$C$10</f>
-        <v>351326.28665642103</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+        <v>358138.37945642107</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D24" s="31">
         <f>D20+D21+D22+D23</f>
-        <v>2761814.9756601988</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+        <v>2815365.5940601984</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="23" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="20" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>93</v>
       </c>
@@ -4830,7 +4862,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>95</v>
       </c>
@@ -4838,7 +4870,7 @@
         <v>7142.1</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
@@ -4847,7 +4879,7 @@
         <v>97206.73000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>97</v>
       </c>
@@ -4855,7 +4887,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="20" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>98</v>
       </c>
@@ -4867,133 +4899,133 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D32" s="31">
         <f>D24+D31</f>
-        <v>2873602.715160199</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+        <v>2927153.3335601985</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="23" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>82</v>
       </c>
       <c r="D35" s="28">
-        <f>Stage1B_Drainage!$F$16</f>
-        <v>29185.192661599995</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+        <f>Stage1B_Drainage!$F$18</f>
+        <v>32375.912661599996</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D36" s="28">
-        <f>Stage1B_Drainage!$F$25</f>
+        <f>Stage1B_Drainage!$F$27</f>
         <v>39331.529377443607</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D37" s="28">
-        <f>Stage1B_Drainage!$F$31</f>
+        <f>Stage1B_Drainage!$F$33</f>
         <v>2942.12</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>85</v>
       </c>
       <c r="D38" s="28">
-        <f>Stage1B_Drainage!$F$37</f>
+        <f>Stage1B_Drainage!$F$39</f>
         <v>2999.2</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D39" s="28">
-        <f>Stage1B_Drainage!$F$40</f>
+        <f>Stage1B_Drainage!$F$42</f>
         <v>5493.3802690582961</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="29" t="s">
         <v>103</v>
       </c>
       <c r="D40" s="30">
         <f>SUM(D35:D39)</f>
-        <v>79951.422308101886</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+        <v>83142.142308101887</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>88</v>
       </c>
       <c r="D41" s="9">
         <f>D40*$C$8</f>
-        <v>4397.328226945604</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+        <v>4572.8178269456039</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>89</v>
       </c>
       <c r="D42" s="9">
         <f>D40*$C$9</f>
-        <v>14391.256015458339</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+        <v>14965.58561545834</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>90</v>
       </c>
       <c r="D43" s="9">
         <f>D40*$C$10</f>
-        <v>14391.256015458339</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="30" x14ac:dyDescent="0.35">
+        <v>14965.58561545834</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="30.6" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D44" s="31">
         <f>D40+D41+D42+D43</f>
-        <v>113131.26256596416</v>
+        <v>117646.13136596419</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D46" s="32">
         <f>D32+D44</f>
-        <v>2986733.9777261633</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+        <v>3044799.4649261627</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B49" s="13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="17" t="s">
         <v>109</v>
@@ -5014,7 +5046,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="30.6" x14ac:dyDescent="0.3">
       <c r="B51" s="16" t="s">
         <v>115</v>
       </c>
@@ -5036,7 +5068,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B52" s="16" t="s">
         <v>118</v>
       </c>
@@ -5058,7 +5090,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B53" s="16" t="s">
         <v>120</v>
       </c>
@@ -5080,7 +5112,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B54" s="16" t="s">
         <v>122</v>
       </c>
@@ -5100,7 +5132,7 @@
       </c>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="1:7" ht="50" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="51" x14ac:dyDescent="0.3">
       <c r="B55" s="16" t="s">
         <v>123</v>
       </c>
@@ -5122,7 +5154,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="30.6" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
         <v>125</v>
       </c>
@@ -5134,8 +5166,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G136"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G138"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -5147,17 +5179,17 @@
     <col min="8" max="8" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>128</v>
       </c>
@@ -5180,12 +5212,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>135</v>
       </c>
@@ -5210,7 +5242,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>139</v>
       </c>
@@ -5236,7 +5268,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>143</v>
       </c>
@@ -5259,7 +5291,7 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>145</v>
       </c>
@@ -5282,7 +5314,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>147</v>
       </c>
@@ -5305,7 +5337,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>149</v>
       </c>
@@ -5328,7 +5360,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>151</v>
       </c>
@@ -5351,7 +5383,7 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>153</v>
       </c>
@@ -5374,7 +5406,7 @@
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>155</v>
       </c>
@@ -5397,7 +5429,7 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>157</v>
       </c>
@@ -5420,7 +5452,7 @@
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>159</v>
       </c>
@@ -5445,7 +5477,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>162</v>
       </c>
@@ -5468,7 +5500,7 @@
       </c>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>164</v>
       </c>
@@ -5493,7 +5525,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>167</v>
       </c>
@@ -5516,7 +5548,7 @@
       </c>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>169</v>
       </c>
@@ -5539,7 +5571,7 @@
       </c>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>171</v>
       </c>
@@ -5562,7 +5594,7 @@
       </c>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>173</v>
       </c>
@@ -5585,7 +5617,7 @@
       </c>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>175</v>
       </c>
@@ -5608,7 +5640,7 @@
       </c>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>177</v>
       </c>
@@ -5631,7 +5663,7 @@
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>179</v>
       </c>
@@ -5654,7 +5686,7 @@
       </c>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>181</v>
       </c>
@@ -5677,7 +5709,7 @@
       </c>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>183</v>
       </c>
@@ -5703,7 +5735,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>186</v>
       </c>
@@ -5727,7 +5759,7 @@
       </c>
       <c r="G28" s="3"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>188</v>
       </c>
@@ -5751,7 +5783,7 @@
       </c>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>190</v>
       </c>
@@ -5775,7 +5807,7 @@
       </c>
       <c r="G30" s="3"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>192</v>
       </c>
@@ -5799,7 +5831,7 @@
       </c>
       <c r="G31" s="3"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>194</v>
       </c>
@@ -5823,7 +5855,7 @@
       </c>
       <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>196</v>
       </c>
@@ -5846,7 +5878,7 @@
       </c>
       <c r="G33" s="3"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>198</v>
       </c>
@@ -5869,7 +5901,7 @@
       </c>
       <c r="G34" s="3"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>200</v>
       </c>
@@ -5892,7 +5924,7 @@
       </c>
       <c r="G35" s="3"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>202</v>
       </c>
@@ -5915,7 +5947,7 @@
       </c>
       <c r="G36" s="3"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>204</v>
       </c>
@@ -5938,7 +5970,7 @@
       </c>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>206</v>
       </c>
@@ -5956,12 +5988,12 @@
         <v>1800.63</v>
       </c>
       <c r="F38" s="9">
-        <f t="shared" ref="F38:F69" si="1">C38*E38</f>
+        <f t="shared" ref="F38:F66" si="1">C38*E38</f>
         <v>14405.04</v>
       </c>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>208</v>
       </c>
@@ -5984,7 +6016,7 @@
       </c>
       <c r="G39" s="3"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>210</v>
       </c>
@@ -6007,7 +6039,7 @@
       </c>
       <c r="G40" s="3"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>212</v>
       </c>
@@ -6030,7 +6062,7 @@
       </c>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>214</v>
       </c>
@@ -6053,7 +6085,7 @@
       </c>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>216</v>
       </c>
@@ -6076,7 +6108,7 @@
       </c>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>218</v>
       </c>
@@ -6099,7 +6131,7 @@
       </c>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>220</v>
       </c>
@@ -6122,7 +6154,7 @@
       </c>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>222</v>
       </c>
@@ -6145,7 +6177,7 @@
       </c>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>224</v>
       </c>
@@ -6168,7 +6200,7 @@
       </c>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>226</v>
       </c>
@@ -6193,7 +6225,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>229</v>
       </c>
@@ -6218,7 +6250,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>232</v>
       </c>
@@ -6241,7 +6273,7 @@
       </c>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>234</v>
       </c>
@@ -6264,7 +6296,7 @@
       </c>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>236</v>
       </c>
@@ -6287,7 +6319,7 @@
       </c>
       <c r="G52" s="3"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>238</v>
       </c>
@@ -6310,7 +6342,7 @@
       </c>
       <c r="G53" s="3"/>
     </row>
-    <row r="54" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>240</v>
       </c>
@@ -6335,7 +6367,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>243</v>
       </c>
@@ -6360,7 +6392,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>246</v>
       </c>
@@ -6383,7 +6415,7 @@
       </c>
       <c r="G56" s="3"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>248</v>
       </c>
@@ -6406,7 +6438,7 @@
       </c>
       <c r="G57" s="3"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>250</v>
       </c>
@@ -6429,7 +6461,7 @@
       </c>
       <c r="G58" s="3"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>252</v>
       </c>
@@ -6455,7 +6487,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>255</v>
       </c>
@@ -6479,7 +6511,7 @@
       </c>
       <c r="G60" s="3"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>257</v>
       </c>
@@ -6503,7 +6535,7 @@
       </c>
       <c r="G61" s="3"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>259</v>
       </c>
@@ -6527,7 +6559,7 @@
       </c>
       <c r="G62" s="3"/>
     </row>
-    <row r="63" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>262</v>
       </c>
@@ -6553,276 +6585,284 @@
         <v>264</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="91.8" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
+        <v>937</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>938</v>
+      </c>
+      <c r="C64" s="45">
+        <f>ROUND(C54*0.1226+C55*0.1255,1)</f>
+        <v>68.900000000000006</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E64" s="28">
+        <f>Materials_Master!$H$75</f>
+        <v>400</v>
+      </c>
+      <c r="F64" s="9">
+        <f>C64*E64</f>
+        <v>27560.000000000004</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="71.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A65" s="13" t="s">
+        <v>940</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>941</v>
+      </c>
+      <c r="C65" s="34">
+        <f>ROUND((C54*0.08+C55*0.075)*2.1,0)</f>
+        <v>94</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E65" s="28">
+        <f>Materials_Master!$H$77</f>
+        <v>48</v>
+      </c>
+      <c r="F65" s="9">
+        <f>C65*E65</f>
+        <v>4512</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B66" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="C64" s="18">
+      <c r="C66" s="18">
         <v>1</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E64" s="28">
+      <c r="E66" s="28">
         <f>Materials_Master!$H$78</f>
         <v>2500</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F66" s="9">
         <f t="shared" si="1"/>
         <v>2500</v>
       </c>
-      <c r="G64" s="3"/>
-    </row>
-    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.35">
-      <c r="A65" s="13" t="s">
+      <c r="G66" s="3"/>
+    </row>
+    <row r="67" spans="1:7" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B65" s="35" t="s">
+      <c r="B67" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="C65" s="18">
+      <c r="C67" s="18">
         <v>0</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D67" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F65" s="36">
+      <c r="F67" s="36">
         <v>0</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G67" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="13" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B68" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="C66" s="18">
+      <c r="C68" s="18">
         <v>35</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D68" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E66" s="28">
+      <c r="E68" s="28">
         <f>Materials_Master!$H$65</f>
         <v>852</v>
       </c>
-      <c r="F66" s="9">
-        <f t="shared" ref="F66:F71" si="2">C66*E66</f>
+      <c r="F68" s="9">
+        <f t="shared" ref="F68:F73" si="2">C68*E68</f>
         <v>29820</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G68" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="13" t="s">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B69" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C69" s="18">
         <v>11</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D69" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E67" s="28">
+      <c r="E69" s="28">
         <f>Materials_Master!$H$66</f>
         <v>1133.1599999999999</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F69" s="9">
         <f t="shared" si="2"/>
         <v>12464.759999999998</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G69" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="13" t="s">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B70" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="C68" s="18">
+      <c r="C70" s="18">
         <v>1</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D70" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E68" s="28">
+      <c r="E70" s="28">
         <f>Materials_Master!$H$67</f>
         <v>4500</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F70" s="9">
         <f t="shared" si="2"/>
         <v>4500</v>
       </c>
-      <c r="G68" s="3"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="13" t="s">
+      <c r="G70" s="3"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B71" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C69" s="18">
+      <c r="C71" s="18">
         <v>1</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D71" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E69" s="28">
+      <c r="E71" s="28">
         <f>Materials_Master!$H$68</f>
         <v>1500</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F71" s="9">
         <f t="shared" si="2"/>
         <v>1500</v>
       </c>
-      <c r="G69" s="3"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="13" t="s">
+      <c r="G71" s="3"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B72" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="C70" s="18">
+      <c r="C72" s="18">
         <v>1</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D72" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E70" s="28">
+      <c r="E72" s="28">
         <f>Materials_Master!$H$69</f>
         <v>5700</v>
       </c>
-      <c r="F70" s="9">
+      <c r="F72" s="9">
         <f t="shared" si="2"/>
         <v>5700</v>
       </c>
-      <c r="G70" s="3"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="13" t="s">
+      <c r="G72" s="3"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B73" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="C71" s="18">
+      <c r="C73" s="18">
         <v>1</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D73" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E71" s="28">
+      <c r="E73" s="28">
         <f>Materials_Master!$H$70</f>
         <v>3000</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F73" s="9">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="G71" s="3"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B72" s="29" t="s">
+      <c r="G73" s="3"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B74" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="F72" s="30">
-        <f>SUM(F6:F71)</f>
-        <v>745994.02447054279</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B73" s="14" t="s">
+      <c r="F74" s="30">
+        <f>SUM(F6:F73)</f>
+        <v>778066.02447054279</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B75" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="F73" s="9">
-        <f>F72*(Materials_Master!$D$8-1)</f>
-        <v>134278.92440469767</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B74" s="29" t="s">
+      <c r="F75" s="9">
+        <f>F74*(Materials_Master!$D$8-1)</f>
+        <v>140051.88440469766</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B76" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="F74" s="30">
-        <f>F72+F73</f>
-        <v>880272.94887524052</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B76" s="23" t="s">
+      <c r="F76" s="30">
+        <f>F74+F75</f>
+        <v>918117.90887524048</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B78" s="23" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77" s="13" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B79" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C77" s="33">
+      <c r="C79" s="33">
         <v>3</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E77" s="28">
-        <f>LabourRates_Master!$G$15</f>
-        <v>2862.42609924812</v>
-      </c>
-      <c r="F77" s="9">
-        <f t="shared" ref="F77:F102" si="3">C77*E77</f>
-        <v>8587.2782977443603</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="B78" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="C78" s="33">
-        <v>3</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E78" s="28">
-        <f>LabourRates_Master!$G$15</f>
-        <v>2862.42609924812</v>
-      </c>
-      <c r="F78" s="9">
-        <f t="shared" si="3"/>
-        <v>8587.2782977443603</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A79" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="B79" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="C79" s="33">
-        <v>16</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>293</v>
@@ -6832,19 +6872,19 @@
         <v>2862.42609924812</v>
       </c>
       <c r="F79" s="9">
-        <f t="shared" si="3"/>
-        <v>45798.817587969919</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+        <f t="shared" ref="F79:F104" si="3">C79*E79</f>
+        <v>8587.2782977443603</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C80" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>293</v>
@@ -6855,18 +6895,18 @@
       </c>
       <c r="F80" s="9">
         <f t="shared" si="3"/>
-        <v>2862.42609924812</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8587.2782977443603</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C81" s="33">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>293</v>
@@ -6877,18 +6917,18 @@
       </c>
       <c r="F81" s="9">
         <f t="shared" si="3"/>
-        <v>28624.260992481199</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45798.817587969919</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C82" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>293</v>
@@ -6899,18 +6939,18 @@
       </c>
       <c r="F82" s="9">
         <f t="shared" si="3"/>
-        <v>5724.8521984962399</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2862.42609924812</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C83" s="33">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>293</v>
@@ -6921,18 +6961,18 @@
       </c>
       <c r="F83" s="9">
         <f t="shared" si="3"/>
-        <v>11449.70439699248</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>28624.260992481199</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C84" s="33">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>293</v>
@@ -6943,15 +6983,15 @@
       </c>
       <c r="F84" s="9">
         <f t="shared" si="3"/>
-        <v>28624.260992481199</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5724.8521984962399</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C85" s="33">
         <v>4</v>
@@ -6968,15 +7008,15 @@
         <v>11449.70439699248</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A86" s="13" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C86" s="33">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>293</v>
@@ -6987,15 +7027,15 @@
       </c>
       <c r="F86" s="9">
         <f t="shared" si="3"/>
-        <v>8587.2782977443603</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+        <v>28624.260992481199</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C87" s="33">
         <v>4</v>
@@ -7012,15 +7052,15 @@
         <v>11449.70439699248</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C88" s="33">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>293</v>
@@ -7031,18 +7071,18 @@
       </c>
       <c r="F88" s="9">
         <f t="shared" si="3"/>
-        <v>62973.37418345864</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8587.2782977443603</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C89" s="33">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>293</v>
@@ -7053,18 +7093,18 @@
       </c>
       <c r="F89" s="9">
         <f t="shared" si="3"/>
-        <v>37211.539290225563</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11449.70439699248</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C90" s="33">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>293</v>
@@ -7075,18 +7115,18 @@
       </c>
       <c r="F90" s="9">
         <f t="shared" si="3"/>
-        <v>17174.556595488721</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+        <v>62973.37418345864</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C91" s="33">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>293</v>
@@ -7097,18 +7137,18 @@
       </c>
       <c r="F91" s="9">
         <f t="shared" si="3"/>
-        <v>5724.8521984962399</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+        <v>37211.539290225563</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C92" s="33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>293</v>
@@ -7119,18 +7159,18 @@
       </c>
       <c r="F92" s="9">
         <f t="shared" si="3"/>
-        <v>20036.982694736838</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17174.556595488721</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C93" s="33">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>293</v>
@@ -7141,18 +7181,18 @@
       </c>
       <c r="F93" s="9">
         <f t="shared" si="3"/>
-        <v>28624.260992481199</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="26" x14ac:dyDescent="0.35">
+        <v>5724.8521984962399</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="B94" s="35" t="s">
-        <v>327</v>
-      </c>
-      <c r="C94" s="37">
-        <v>0</v>
+        <v>322</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="C94" s="33">
+        <v>7</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>293</v>
@@ -7163,18 +7203,18 @@
       </c>
       <c r="F94" s="9">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+        <v>20036.982694736838</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C95" s="33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>293</v>
@@ -7185,18 +7225,18 @@
       </c>
       <c r="F95" s="9">
         <f t="shared" si="3"/>
-        <v>25761.834893233081</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+        <v>28624.260992481199</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="B96" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="C96" s="33">
-        <v>6</v>
+        <v>326</v>
+      </c>
+      <c r="B96" s="35" t="s">
+        <v>327</v>
+      </c>
+      <c r="C96" s="37">
+        <v>0</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>293</v>
@@ -7207,15 +7247,15 @@
       </c>
       <c r="F96" s="9">
         <f t="shared" si="3"/>
-        <v>17174.556595488721</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C97" s="33">
         <v>9</v>
@@ -7232,15 +7272,15 @@
         <v>25761.834893233081</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C98" s="33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>293</v>
@@ -7251,18 +7291,18 @@
       </c>
       <c r="F98" s="9">
         <f t="shared" si="3"/>
-        <v>22899.40879398496</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+        <v>17174.556595488721</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C99" s="33">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>293</v>
@@ -7273,15 +7313,15 @@
       </c>
       <c r="F99" s="9">
         <f t="shared" si="3"/>
-        <v>45798.817587969919</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+        <v>25761.834893233081</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C100" s="33">
         <v>8</v>
@@ -7298,15 +7338,15 @@
         <v>22899.40879398496</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C101" s="33">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>293</v>
@@ -7317,18 +7357,18 @@
       </c>
       <c r="F101" s="9">
         <f t="shared" si="3"/>
-        <v>65835.800282706754</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+        <v>45798.817587969919</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C102" s="33">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>293</v>
@@ -7339,508 +7379,552 @@
       </c>
       <c r="F102" s="9">
         <f t="shared" si="3"/>
+        <v>22899.40879398496</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A103" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="C103" s="33">
+        <v>23</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E103" s="28">
+        <f>LabourRates_Master!$G$15</f>
+        <v>2862.42609924812</v>
+      </c>
+      <c r="F103" s="9">
+        <f t="shared" si="3"/>
+        <v>65835.800282706754</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C104" s="33">
+        <v>13</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E104" s="28">
+        <f>LabourRates_Master!$G$15</f>
+        <v>2862.42609924812</v>
+      </c>
+      <c r="F104" s="9">
+        <f t="shared" si="3"/>
         <v>37211.539290225563</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B103" s="29" t="s">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B105" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="C103" s="38">
-        <f>SUM(C77:C102)</f>
+      <c r="C105" s="38">
+        <f>SUM(C79:C104)</f>
         <v>212</v>
       </c>
-      <c r="F103" s="30">
-        <f>SUM(F77:F102)</f>
+      <c r="F105" s="30">
+        <f>SUM(F79:F104)</f>
         <v>606834.33304060157</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A104" s="13" t="s">
+    <row r="106" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="A106" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B106" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="C104" s="19">
-        <f>ROUND(120*C103/(C103+Stage1B_Drainage!$C$23),1)</f>
+      <c r="C106" s="19">
+        <f>ROUND(120*C105/(C105+Stage1B_Drainage!$C$25),1)</f>
         <v>114.1</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D106" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="E104" s="28">
+      <c r="E106" s="28">
         <f>LabourRates_Master!$G$11</f>
         <v>1329.6342857142859</v>
       </c>
-      <c r="F104" s="9">
-        <f>C104*E104</f>
+      <c r="F106" s="9">
+        <f>C106*E106</f>
         <v>151711.272</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="20" x14ac:dyDescent="0.35">
-      <c r="B105" s="29" t="s">
+    <row r="107" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B107" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="F105" s="30">
-        <f>F103+F104</f>
+      <c r="F107" s="30">
+        <f>F105+F106</f>
         <v>758545.60504060157</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="G107" s="3" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B107" s="23" t="s">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B109" s="23" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B108" s="16" t="s">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B110" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="C108" s="33">
+      <c r="C110" s="33">
         <v>43</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D110" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E108" s="28">
+      <c r="E110" s="28">
         <f>Equip_Master!$D$5</f>
         <v>317.2</v>
       </c>
-      <c r="F108" s="9">
-        <f t="shared" ref="F108:F122" si="4">C108*E108</f>
+      <c r="F110" s="9">
+        <f t="shared" ref="F110:F124" si="4">C110*E110</f>
         <v>13639.6</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B109" s="16" t="s">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B111" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="C109" s="33">
+      <c r="C111" s="33">
         <v>64</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D111" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E109" s="28">
+      <c r="E111" s="28">
         <f>Equip_Master!$D$6</f>
         <v>261.17</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F111" s="9">
         <f t="shared" si="4"/>
         <v>16714.88</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B110" s="16" t="s">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B112" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="C110" s="33">
+      <c r="C112" s="33">
         <v>66</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D112" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E110" s="28">
+      <c r="E112" s="28">
         <f>Equip_Master!$D$7</f>
         <v>314.29000000000002</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F112" s="9">
         <f t="shared" si="4"/>
         <v>20743.140000000003</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B111" s="16" t="s">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B113" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="C111" s="33">
+      <c r="C113" s="33">
         <v>56</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D113" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E111" s="28">
+      <c r="E113" s="28">
         <f>Equip_Master!$D$8</f>
         <v>238.67</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F113" s="9">
         <f t="shared" si="4"/>
         <v>13365.519999999999</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="G113" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B112" s="16" t="s">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B114" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="C112" s="33">
+      <c r="C114" s="33">
         <v>10</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D114" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E112" s="28">
+      <c r="E114" s="28">
         <f>Equip_Master!$D$9</f>
         <v>203</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F114" s="9">
         <f t="shared" si="4"/>
         <v>2030</v>
       </c>
     </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B113" s="16" t="s">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B115" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="C113" s="33">
+      <c r="C115" s="33">
         <v>60</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D115" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E113" s="28">
+      <c r="E115" s="28">
         <f>Equip_Master!$D$10</f>
         <v>165</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F115" s="9">
         <f t="shared" si="4"/>
         <v>9900</v>
       </c>
     </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B114" s="16" t="s">
+    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B116" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="C114" s="33">
+      <c r="C116" s="33">
         <v>70</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D116" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E114" s="28">
+      <c r="E116" s="28">
         <f>Equip_Master!$D$11</f>
         <v>34.29</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F116" s="9">
         <f t="shared" si="4"/>
         <v>2400.2999999999997</v>
       </c>
     </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B115" s="16" t="s">
+    <row r="117" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B117" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="C115" s="33">
+      <c r="C117" s="33">
         <v>69</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D117" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E115" s="28">
+      <c r="E117" s="28">
         <f>Equip_Master!$D$12</f>
         <v>171.43</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F117" s="9">
         <f t="shared" si="4"/>
         <v>11828.67</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G117" s="3" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B116" s="16" t="s">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B118" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="C116" s="33">
+      <c r="C118" s="33">
         <v>8</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D118" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E116" s="28">
+      <c r="E118" s="28">
         <f>Equip_Master!$D$16</f>
         <v>3800</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F118" s="9">
         <f t="shared" si="4"/>
         <v>30400</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G118" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B117" s="16" t="s">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B119" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="C117" s="33">
+      <c r="C119" s="33">
         <v>17</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D119" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E117" s="28">
+      <c r="E119" s="28">
         <f>Equip_Master!$D$17</f>
         <v>2200</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F119" s="9">
         <f t="shared" si="4"/>
         <v>37400</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G119" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B118" s="16" t="s">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B120" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="C118" s="33">
+      <c r="C120" s="33">
         <v>14</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D120" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E118" s="28">
+      <c r="E120" s="28">
         <f>Equip_Master!$D$18</f>
         <v>120</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F120" s="9">
         <f t="shared" si="4"/>
         <v>1680</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G120" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B119" s="16" t="s">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B121" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="C119" s="33">
+      <c r="C121" s="33">
         <v>6</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D121" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E119" s="28">
+      <c r="E121" s="28">
         <f>Equip_Master!$D$13</f>
         <v>295.77</v>
       </c>
-      <c r="F119" s="9">
+      <c r="F121" s="9">
         <f t="shared" si="4"/>
         <v>1774.62</v>
       </c>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B120" s="16" t="s">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B122" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="C120" s="33">
+      <c r="C122" s="33">
         <v>2</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="D122" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E120" s="28">
+      <c r="E122" s="28">
         <f>Equip_Master!$D$15</f>
         <v>1100</v>
       </c>
-      <c r="F120" s="9">
+      <c r="F122" s="9">
         <f t="shared" si="4"/>
         <v>2200</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G122" s="3" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B121" s="16" t="s">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B123" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="C121" s="33">
+      <c r="C123" s="33">
         <v>10</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D123" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E121" s="28">
+      <c r="E123" s="28">
         <f>Equip_Master!$D$14</f>
         <v>57</v>
       </c>
-      <c r="F121" s="9">
+      <c r="F123" s="9">
         <f t="shared" si="4"/>
         <v>570</v>
       </c>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B122" s="16" t="s">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B124" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="C122" s="33">
+      <c r="C124" s="33">
         <v>5</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D124" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E122" s="28">
+      <c r="E124" s="28">
         <f>Equip_Master!$D$19</f>
         <v>100</v>
       </c>
-      <c r="F122" s="9">
+      <c r="F124" s="9">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B123" s="29" t="s">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B125" s="29" t="s">
         <v>372</v>
       </c>
-      <c r="F123" s="30">
-        <f>SUM(F108:F122)</f>
+      <c r="F125" s="30">
+        <f>SUM(F110:F124)</f>
         <v>165146.73000000001</v>
       </c>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B125" s="23" t="s">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B127" s="23" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B126" s="16" t="s">
+    <row r="128" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B128" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="C126" s="33">
+      <c r="C128" s="33">
         <v>5</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D128" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E126" s="28">
+      <c r="E128" s="28">
         <f>Materials_Master!$H$83</f>
         <v>2070</v>
       </c>
-      <c r="F126" s="9">
-        <f>C126*E126</f>
+      <c r="F128" s="9">
+        <f>C128*E128</f>
         <v>10350</v>
       </c>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B127" s="16" t="s">
+    <row r="129" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B129" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="C127" s="33">
+      <c r="C129" s="33">
         <v>1</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="D129" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E127" s="28">
+      <c r="E129" s="28">
         <f>Materials_Master!$H$84</f>
         <v>1494.9999999999998</v>
       </c>
-      <c r="F127" s="9">
-        <f>C127*E127</f>
+      <c r="F129" s="9">
+        <f>C129*E129</f>
         <v>1494.9999999999998</v>
       </c>
     </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B128" s="16" t="s">
+    <row r="130" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B130" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="33">
+      <c r="C130" s="33">
         <v>40</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="D130" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="E128" s="28">
+      <c r="E130" s="28">
         <f>Materials_Master!$H$85</f>
         <v>140.29999999999998</v>
       </c>
-      <c r="F128" s="9">
-        <f>C128*E128</f>
+      <c r="F130" s="9">
+        <f>C130*E130</f>
         <v>5611.9999999999991</v>
       </c>
     </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B129" s="16" t="s">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B131" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="C129" s="33">
+      <c r="C131" s="33">
         <v>4</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="D131" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="E129" s="28">
+      <c r="E131" s="28">
         <f>Materials_Master!$H$86</f>
         <v>977.49999999999989</v>
       </c>
-      <c r="F129" s="9">
-        <f>C129*E129</f>
+      <c r="F131" s="9">
+        <f>C131*E131</f>
         <v>3909.9999999999995</v>
       </c>
     </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B130" s="16" t="s">
+    <row r="132" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B132" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="C130" s="34">
+      <c r="C132" s="34">
         <f>ROUND(0.21*(C6+C8+C10+C11+C12+C13+C14+C16+C17+C18)+0.8*130.76,0)</f>
         <v>448</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D132" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E130" s="28">
+      <c r="E132" s="28">
         <f>Materials_Master!$H$87</f>
         <v>46</v>
       </c>
-      <c r="F130" s="9">
-        <f>C130*E130</f>
+      <c r="F132" s="9">
+        <f>C132*E132</f>
         <v>20608</v>
       </c>
-      <c r="G130" s="13" t="s">
+      <c r="G132" s="13" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B131" s="29" t="s">
+    <row r="133" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B133" s="29" t="s">
         <v>382</v>
       </c>
-      <c r="F131" s="30">
-        <f>SUM(F126:F130)</f>
+      <c r="F133" s="30">
+        <f>SUM(F128:F132)</f>
         <v>41975</v>
       </c>
     </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B133" s="23" t="s">
+    <row r="135" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B135" s="23" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B134" s="4" t="s">
+    <row r="136" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B136" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="F134" s="28">
-        <f>Accommodation!$E$27*C103/(C103+Stage1B_Drainage!$C$23)</f>
+      <c r="F136" s="28">
+        <f>Accommodation!$E$27*C105/(C105+Stage1B_Drainage!$C$25)</f>
         <v>105872.41973094171</v>
       </c>
     </row>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B136" s="2" t="s">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B138" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F136" s="31">
-        <f>F74+F105+F123+F131+F134</f>
-        <v>1951812.7036467837</v>
+      <c r="F138" s="31">
+        <f>F76+F107+F125+F133+F136</f>
+        <v>1989657.6636467837</v>
       </c>
     </row>
   </sheetData>
@@ -7850,8 +7934,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -7863,17 +7947,17 @@
     <col min="8" max="8" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="30.6" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>128</v>
       </c>
@@ -7896,12 +7980,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>135</v>
       </c>
@@ -7919,12 +8003,12 @@
         <v>50.62299999999999</v>
       </c>
       <c r="F6" s="9">
-        <f t="shared" ref="F6:F13" si="0">C6*E6</f>
+        <f t="shared" ref="F6:F15" si="0">C6*E6</f>
         <v>1498.4407999999999</v>
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>240</v>
       </c>
@@ -7949,7 +8033,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>243</v>
       </c>
@@ -7974,7 +8058,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>246</v>
       </c>
@@ -7997,7 +8081,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>248</v>
       </c>
@@ -8020,7 +8104,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>259</v>
       </c>
@@ -8044,137 +8128,145 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>943</v>
+      </c>
+      <c r="C12" s="45">
+        <f>ROUND(C8*0.1226+C7*0.1255,1)</f>
+        <v>5.8</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="28">
+        <f>Materials_Master!$H$75</f>
+        <v>400</v>
+      </c>
+      <c r="F12" s="9">
+        <f>C12*E12</f>
+        <v>2320</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="C13" s="19">
+        <f>ROUND((C8*0.08+C7*0.075)*2.1,0)</f>
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" s="28">
+        <f>Materials_Master!$H$77</f>
+        <v>48</v>
+      </c>
+      <c r="F13" s="9">
+        <f>C13*E13</f>
+        <v>384</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B14" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C14" s="18">
         <v>1</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E14" s="28">
         <f>Materials_Master!$H$66</f>
         <v>1133.1599999999999</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F14" s="9">
         <f t="shared" si="0"/>
         <v>1133.1599999999999</v>
       </c>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B15" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C15" s="18">
         <v>1</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E15" s="28">
         <f>Materials_Master!$H$71</f>
         <v>600</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F15" s="9">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B14" s="29" t="s">
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="F14" s="30">
-        <f>SUM(F6:F13)</f>
-        <v>24733.214119999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B15" s="14" t="s">
+      <c r="F16" s="30">
+        <f>SUM(F6:F15)</f>
+        <v>27437.214119999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="F15" s="9">
-        <f>F14*(Materials_Master!$D$8-1)</f>
-        <v>4451.9785415999977</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B16" s="29" t="s">
+      <c r="F17" s="9">
+        <f>F16*(Materials_Master!$D$8-1)</f>
+        <v>4938.698541599998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="F16" s="30">
-        <f>F14+F15</f>
-        <v>29185.192661599995</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="23" t="s">
+      <c r="F18" s="30">
+        <f>F16+F17</f>
+        <v>32375.912661599996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="23" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B21" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C21" s="33">
         <v>2</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E19" s="28">
-        <f>LabourRates_Master!$G$15</f>
-        <v>2862.42609924812</v>
-      </c>
-      <c r="F19" s="9">
-        <f>C19*E19</f>
-        <v>5724.8521984962399</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>402</v>
-      </c>
-      <c r="C20" s="33">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E20" s="28">
-        <f>LabourRates_Master!$G$15</f>
-        <v>2862.42609924812</v>
-      </c>
-      <c r="F20" s="9">
-        <f>C20*E20</f>
-        <v>5724.8521984962399</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>404</v>
-      </c>
-      <c r="C21" s="33">
-        <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>293</v>
@@ -8185,18 +8277,18 @@
       </c>
       <c r="F21" s="9">
         <f>C21*E21</f>
-        <v>8587.2782977443603</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5724.8521984962399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C22" s="33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>293</v>
@@ -8207,218 +8299,262 @@
       </c>
       <c r="F22" s="9">
         <f>C22*E22</f>
+        <v>5724.8521984962399</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="C23" s="33">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E23" s="28">
+        <f>LabourRates_Master!$G$15</f>
+        <v>2862.42609924812</v>
+      </c>
+      <c r="F23" s="9">
+        <f>C23*E23</f>
+        <v>8587.2782977443603</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="C24" s="33">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E24" s="28">
+        <f>LabourRates_Master!$G$15</f>
+        <v>2862.42609924812</v>
+      </c>
+      <c r="F24" s="9">
+        <f>C24*E24</f>
         <v>11449.70439699248</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="29" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="C23" s="38">
-        <f>SUM(C19:C22)</f>
+      <c r="C25" s="38">
+        <f>SUM(C21:C24)</f>
         <v>11</v>
       </c>
-      <c r="F23" s="30">
-        <f>SUM(F19:F22)</f>
+      <c r="F25" s="30">
+        <f>SUM(F21:F24)</f>
         <v>31486.68709172932</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="13" t="s">
+    <row r="26" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B26" s="16" t="s">
         <v>407</v>
       </c>
-      <c r="C24" s="19">
-        <f>ROUND(120*C23/(Stage1A_Drainage!$C$103+C23),1)</f>
+      <c r="C26" s="19">
+        <f>ROUND(120*C25/(Stage1A_Drainage!$C$105+C25),1)</f>
         <v>5.9</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E26" s="28">
         <f>LabourRates_Master!$G$11</f>
         <v>1329.6342857142859</v>
       </c>
-      <c r="F24" s="9">
-        <f>C24*E24</f>
+      <c r="F26" s="9">
+        <f>C26*E26</f>
         <v>7844.8422857142868</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="29" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="F25" s="30">
-        <f>F23+F24</f>
+      <c r="F27" s="30">
+        <f>F25+F26</f>
         <v>39331.529377443607</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="23" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="23" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="4" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C30" s="33">
         <v>7</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E30" s="28">
         <f>Equip_Master!$D$8</f>
         <v>238.67</v>
       </c>
-      <c r="F28" s="9">
-        <f>C28*E28</f>
+      <c r="F30" s="9">
+        <f>C30*E30</f>
         <v>1670.6899999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="4" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C31" s="33">
         <v>1</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E31" s="28">
         <f>Equip_Master!$D$12</f>
         <v>171.43</v>
       </c>
-      <c r="F29" s="9">
-        <f>C29*E29</f>
+      <c r="F31" s="9">
+        <f>C31*E31</f>
         <v>171.43</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="4" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C32" s="33">
         <v>1</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E30" s="28">
+      <c r="E32" s="28">
         <f>Equip_Master!$D$15</f>
         <v>1100</v>
       </c>
-      <c r="F30" s="9">
-        <f>C30*E30</f>
+      <c r="F32" s="9">
+        <f>C32*E32</f>
         <v>1100</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B31" s="29" t="s">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="29" t="s">
         <v>372</v>
       </c>
-      <c r="F31" s="30">
-        <f>SUM(F28:F30)</f>
+      <c r="F33" s="30">
+        <f>SUM(F30:F32)</f>
         <v>2942.12</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="23" t="s">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="23" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B34" s="4" t="s">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C36" s="33">
         <v>1</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E34" s="28">
+      <c r="E36" s="28">
         <f>Materials_Master!$H$83</f>
         <v>2070</v>
       </c>
-      <c r="F34" s="9">
-        <f>C34*E34</f>
+      <c r="F36" s="9">
+        <f>C36*E36</f>
         <v>2070</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B35" s="4" t="s">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C37" s="33">
         <v>4</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="E35" s="28">
+      <c r="E37" s="28">
         <f>Materials_Master!$H$85</f>
         <v>140.29999999999998</v>
       </c>
-      <c r="F35" s="9">
-        <f>C35*E35</f>
+      <c r="F37" s="9">
+        <f>C37*E37</f>
         <v>561.19999999999993</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="4" t="s">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C38" s="34">
         <f>ROUND(0.21*C6+2,0)</f>
         <v>8</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="28">
+      <c r="E38" s="28">
         <f>Materials_Master!$H$87</f>
         <v>46</v>
       </c>
-      <c r="F36" s="9">
-        <f>C36*E36</f>
+      <c r="F38" s="9">
+        <f>C38*E38</f>
         <v>368</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="29" t="s">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="29" t="s">
         <v>382</v>
       </c>
-      <c r="F37" s="30">
-        <f>SUM(F34:F36)</f>
+      <c r="F39" s="30">
+        <f>SUM(F36:F38)</f>
         <v>2999.2</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="23" t="s">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="23" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B40" s="4" t="s">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="F40" s="28">
-        <f>Accommodation!$E$27*C23/(Stage1A_Drainage!$C$103+C23)</f>
+      <c r="F42" s="28">
+        <f>Accommodation!$E$27*C25/(Stage1A_Drainage!$C$105+C25)</f>
         <v>5493.3802690582961</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B42" s="2" t="s">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="F42" s="31">
-        <f>F16+F25+F31+F37+F40</f>
-        <v>79951.422308101886</v>
+      <c r="F44" s="31">
+        <f>F18+F27+F33+F39+F42</f>
+        <v>83142.142308101887</v>
       </c>
     </row>
   </sheetData>
@@ -8429,7 +8565,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -8439,22 +8575,22 @@
     <col min="9" max="9" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>419</v>
       </c>
@@ -8462,7 +8598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>420</v>
       </c>
@@ -8470,7 +8606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>421</v>
       </c>
@@ -8479,7 +8615,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>422</v>
       </c>
@@ -8487,7 +8623,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
         <v>423</v>
@@ -8514,7 +8650,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>431</v>
       </c>
@@ -8544,7 +8680,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>434</v>
       </c>
@@ -8574,7 +8710,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>436</v>
       </c>
@@ -8604,7 +8740,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>438</v>
       </c>
@@ -8627,7 +8763,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="30" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" ht="30.6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>441</v>
       </c>
@@ -8640,7 +8776,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I87"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="56" customWidth="1"/>
@@ -8652,22 +8788,22 @@
     <col min="9" max="9" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="51" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>445</v>
       </c>
@@ -8675,7 +8811,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>446</v>
       </c>
@@ -8683,7 +8819,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>447</v>
       </c>
@@ -8691,7 +8827,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
         <v>448</v>
       </c>
@@ -8699,7 +8835,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>449</v>
       </c>
@@ -8726,7 +8862,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>456</v>
       </c>
@@ -8754,7 +8890,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>460</v>
       </c>
@@ -8781,7 +8917,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>464</v>
       </c>
@@ -8809,7 +8945,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>467</v>
       </c>
@@ -8836,7 +8972,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>471</v>
       </c>
@@ -8865,7 +9001,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>475</v>
       </c>
@@ -8893,7 +9029,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>479</v>
       </c>
@@ -8922,7 +9058,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>483</v>
       </c>
@@ -8950,7 +9086,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>487</v>
       </c>
@@ -8979,7 +9115,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>490</v>
       </c>
@@ -9008,7 +9144,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>494</v>
       </c>
@@ -9037,7 +9173,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>498</v>
       </c>
@@ -9066,7 +9202,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>502</v>
       </c>
@@ -9094,7 +9230,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>506</v>
       </c>
@@ -9122,7 +9258,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>509</v>
       </c>
@@ -9150,7 +9286,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>510</v>
       </c>
@@ -9178,7 +9314,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>512</v>
       </c>
@@ -9206,7 +9342,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>513</v>
       </c>
@@ -9234,7 +9370,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>515</v>
       </c>
@@ -9262,7 +9398,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>518</v>
       </c>
@@ -9289,7 +9425,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>522</v>
       </c>
@@ -9316,7 +9452,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>525</v>
       </c>
@@ -9343,7 +9479,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>528</v>
       </c>
@@ -9370,7 +9506,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>531</v>
       </c>
@@ -9397,7 +9533,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>534</v>
       </c>
@@ -9424,7 +9560,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>536</v>
       </c>
@@ -9451,7 +9587,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>539</v>
       </c>
@@ -9478,7 +9614,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>542</v>
       </c>
@@ -9505,7 +9641,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>545</v>
       </c>
@@ -9532,7 +9668,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>548</v>
       </c>
@@ -9559,7 +9695,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>551</v>
       </c>
@@ -9586,7 +9722,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>554</v>
       </c>
@@ -9613,7 +9749,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>556</v>
       </c>
@@ -9640,7 +9776,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>559</v>
       </c>
@@ -9667,7 +9803,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>561</v>
       </c>
@@ -9694,7 +9830,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>563</v>
       </c>
@@ -9721,7 +9857,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>565</v>
       </c>
@@ -9748,7 +9884,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>567</v>
       </c>
@@ -9775,7 +9911,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>569</v>
       </c>
@@ -9802,7 +9938,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>573</v>
       </c>
@@ -9829,7 +9965,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
         <v>576</v>
       </c>
@@ -9856,7 +9992,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>578</v>
       </c>
@@ -9883,7 +10019,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>580</v>
       </c>
@@ -9910,7 +10046,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>582</v>
       </c>
@@ -9937,7 +10073,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>584</v>
       </c>
@@ -9964,7 +10100,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>587</v>
       </c>
@@ -9991,7 +10127,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>590</v>
       </c>
@@ -10018,7 +10154,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="40" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
         <v>593</v>
       </c>
@@ -10046,7 +10182,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
         <v>597</v>
       </c>
@@ -10074,7 +10210,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
         <v>601</v>
       </c>
@@ -10102,7 +10238,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
         <v>605</v>
       </c>
@@ -10130,7 +10266,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
         <v>607</v>
       </c>
@@ -10158,7 +10294,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="14" t="s">
         <v>609</v>
       </c>
@@ -10186,7 +10322,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
         <v>611</v>
       </c>
@@ -10214,7 +10350,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
         <v>613</v>
       </c>
@@ -10242,7 +10378,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
         <v>617</v>
       </c>
@@ -10270,7 +10406,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A67" s="14" t="s">
         <v>620</v>
       </c>
@@ -10298,7 +10434,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
         <v>624</v>
       </c>
@@ -10326,7 +10462,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A69" s="14" t="s">
         <v>628</v>
       </c>
@@ -10354,7 +10490,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
         <v>632</v>
       </c>
@@ -10382,7 +10518,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
         <v>635</v>
       </c>
@@ -10410,7 +10546,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A72" s="14" t="s">
         <v>638</v>
       </c>
@@ -10437,7 +10573,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
         <v>642</v>
       </c>
@@ -10464,7 +10600,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A74" s="14" t="s">
         <v>644</v>
       </c>
@@ -10491,7 +10627,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A75" s="14" t="s">
         <v>646</v>
       </c>
@@ -10518,7 +10654,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
         <v>649</v>
       </c>
@@ -10545,7 +10681,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="14" t="s">
         <v>653</v>
       </c>
@@ -10572,7 +10708,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A78" s="14" t="s">
         <v>656</v>
       </c>
@@ -10599,7 +10735,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A79" s="14" t="s">
         <v>659</v>
       </c>
@@ -10626,7 +10762,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
         <v>663</v>
       </c>
@@ -10653,7 +10789,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="14" t="s">
         <v>667</v>
       </c>
@@ -10680,7 +10816,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A82" s="14" t="s">
         <v>669</v>
       </c>
@@ -10708,7 +10844,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
         <v>673</v>
       </c>
@@ -10736,7 +10872,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="14" t="s">
         <v>676</v>
       </c>
@@ -10764,7 +10900,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="14" t="s">
         <v>679</v>
       </c>
@@ -10792,7 +10928,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
         <v>682</v>
       </c>
@@ -10820,7 +10956,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
         <v>685</v>
       </c>
@@ -10856,7 +10992,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
@@ -10867,17 +11003,17 @@
     <col min="7" max="7" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="40" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
         <v>450</v>
@@ -10898,7 +11034,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>351</v>
       </c>
@@ -10918,7 +11054,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>353</v>
       </c>
@@ -10938,7 +11074,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>354</v>
       </c>
@@ -10958,7 +11094,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>355</v>
       </c>
@@ -10978,7 +11114,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>357</v>
       </c>
@@ -10998,7 +11134,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>358</v>
       </c>
@@ -11016,7 +11152,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>359</v>
       </c>
@@ -11034,7 +11170,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>360</v>
       </c>
@@ -11052,7 +11188,7 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>367</v>
       </c>
@@ -11072,7 +11208,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>370</v>
       </c>
@@ -11092,7 +11228,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>368</v>
       </c>
@@ -11112,7 +11248,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>362</v>
       </c>
@@ -11132,7 +11268,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>364</v>
       </c>
@@ -11152,7 +11288,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>366</v>
       </c>
@@ -11172,7 +11308,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>371</v>
       </c>
@@ -11192,7 +11328,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>712</v>
       </c>
@@ -11212,12 +11348,12 @@
         <v>715</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="70" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="69" x14ac:dyDescent="0.3">
       <c r="B22" s="21" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17" t="s">
         <v>129</v>
@@ -11236,7 +11372,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
         <v>721</v>
       </c>
@@ -11253,7 +11389,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
         <v>722</v>
       </c>
@@ -11270,7 +11406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
         <v>723</v>
       </c>
@@ -11287,7 +11423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
         <v>724</v>
       </c>
@@ -11304,7 +11440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
         <v>725</v>
       </c>
@@ -11321,7 +11457,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>726</v>
       </c>
@@ -11338,7 +11474,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
         <v>727</v>
       </c>
@@ -11355,7 +11491,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="s">
         <v>728</v>
       </c>
@@ -11372,7 +11508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
         <v>729</v>
       </c>
@@ -11389,7 +11525,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>730</v>
       </c>
@@ -11406,7 +11542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>731</v>
       </c>
@@ -11423,7 +11559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="13" t="s">
         <v>732</v>
       </c>
@@ -11440,7 +11576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="13" t="s">
         <v>733</v>
       </c>
@@ -11457,7 +11593,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="13" t="s">
         <v>734</v>
       </c>
@@ -11474,7 +11610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="s">
         <v>735</v>
       </c>
@@ -11491,7 +11627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="13" t="s">
         <v>736</v>
       </c>
@@ -11508,7 +11644,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="s">
         <v>737</v>
       </c>
@@ -11525,7 +11661,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="13" t="s">
         <v>738</v>
       </c>
@@ -11542,7 +11678,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="13" t="s">
         <v>739</v>
       </c>
@@ -11559,7 +11695,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="13" t="s">
         <v>740</v>
       </c>
@@ -11576,7 +11712,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="13" t="s">
         <v>741</v>
       </c>
@@ -11593,7 +11729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="13" t="s">
         <v>742</v>
       </c>
@@ -11610,7 +11746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="13" t="s">
         <v>743</v>
       </c>
@@ -11627,7 +11763,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="13" t="s">
         <v>744</v>
       </c>
@@ -11644,7 +11780,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="13" t="s">
         <v>745</v>
       </c>
@@ -11661,7 +11797,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="13" t="s">
         <v>746</v>
       </c>
@@ -11678,7 +11814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="13" t="s">
         <v>747</v>
       </c>
@@ -11695,7 +11831,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="13" t="s">
         <v>748</v>
       </c>
@@ -11712,7 +11848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="13" t="s">
         <v>749</v>
       </c>
@@ -11729,7 +11865,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="13" t="s">
         <v>750</v>
       </c>
@@ -11746,7 +11882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="13" t="s">
         <v>751</v>
       </c>
@@ -11763,7 +11899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="13" t="s">
         <v>752</v>
       </c>
@@ -11780,7 +11916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="13" t="s">
         <v>753</v>
       </c>
@@ -11797,7 +11933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" s="13" t="s">
         <v>754</v>
       </c>
@@ -11814,7 +11950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="13" t="s">
         <v>755</v>
       </c>
@@ -11839,7 +11975,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
@@ -11848,17 +11984,17 @@
     <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="40" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>758</v>
       </c>
@@ -11869,7 +12005,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>760</v>
       </c>
@@ -11880,7 +12016,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>762</v>
       </c>
@@ -11888,7 +12024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>763</v>
       </c>
@@ -11899,7 +12035,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>765</v>
       </c>
@@ -11907,7 +12043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
         <v>766</v>
@@ -11928,7 +12064,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>772</v>
       </c>
@@ -11952,7 +12088,7 @@
         <v>25811.699999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>773</v>
       </c>
@@ -11976,7 +12112,7 @@
         <v>25811.699999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>774</v>
       </c>
@@ -12000,7 +12136,7 @@
         <v>18068.189999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>775</v>
       </c>
@@ -12024,7 +12160,7 @@
         <v>10324.679999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>776</v>
       </c>
@@ -12048,7 +12184,7 @@
         <v>18068.189999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>777</v>
       </c>
@@ -12072,7 +12208,7 @@
         <v>18068.189999999999</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="29" t="s">
         <v>778</v>
       </c>
@@ -12097,7 +12233,7 @@
         <v>116152.65</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>779</v>
       </c>
@@ -12110,7 +12246,7 @@
         <v>15487.019999999999</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>780</v>
       </c>
@@ -12119,7 +12255,7 @@
         <v>75365.8</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>781</v>
       </c>
@@ -12128,7 +12264,7 @@
         <v>116152.65</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>782</v>
       </c>
@@ -12137,7 +12273,7 @@
         <v>40786.849999999991</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>783</v>
       </c>
@@ -12146,7 +12282,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="29" t="s">
         <v>784</v>
       </c>
@@ -12163,7 +12299,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="66" customWidth="1"/>
@@ -12173,17 +12309,17 @@
     <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="61.2" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
         <v>450</v>
@@ -12204,12 +12340,12 @@
         <v>787</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="23" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="50" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="51" x14ac:dyDescent="0.3">
       <c r="B6" s="16" t="s">
         <v>789</v>
       </c>
@@ -12231,12 +12367,12 @@
         <v>790</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="23" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
         <v>792</v>
       </c>
@@ -12257,7 +12393,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
         <v>794</v>
       </c>
@@ -12278,7 +12414,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
         <v>797</v>
       </c>
@@ -12299,7 +12435,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
         <v>799</v>
       </c>
@@ -12320,7 +12456,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
         <v>801</v>
       </c>
@@ -12341,7 +12477,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
         <v>802</v>
       </c>
@@ -12362,7 +12498,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
         <v>803</v>
       </c>
@@ -12383,7 +12519,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
         <v>805</v>
       </c>
@@ -12404,12 +12540,12 @@
         <v>806</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="23" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="16" t="s">
         <v>808</v>
       </c>
@@ -12430,7 +12566,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>811</v>
       </c>
@@ -12451,7 +12587,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="16" t="s">
         <v>813</v>
       </c>
@@ -12472,7 +12608,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="16" t="s">
         <v>815</v>
       </c>
@@ -12493,12 +12629,12 @@
         <v>816</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="20" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
         <v>818</v>
       </c>
@@ -12519,12 +12655,12 @@
         <v>819</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="23" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="25" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B24" s="16" t="s">
         <v>821</v>
       </c>
@@ -12547,7 +12683,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>823</v>
       </c>
@@ -12568,12 +12704,12 @@
         <v>824</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:7" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
         <v>825</v>
       </c>
       <c r="C26" s="33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>267</v>
@@ -12583,15 +12719,15 @@
       </c>
       <c r="F26" s="9">
         <f>C26*E26</f>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="16" t="s">
         <v>826</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="16" t="s">
-        <v>827</v>
       </c>
       <c r="C27" s="33">
         <v>1</v>
@@ -12607,62 +12743,62 @@
         <v>2500</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="29" t="s">
         <v>828</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="29" t="s">
-        <v>829</v>
       </c>
       <c r="F29" s="30">
         <f>SUM(F5:F27)</f>
-        <v>62561.25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+        <v>59061.25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="14" t="s">
+        <v>829</v>
+      </c>
+      <c r="F31" s="12">
+        <f>0.055*(Stage1A_Drainage!$F$138+Stage1B_Drainage!$F$44)</f>
+        <v>114003.98932751871</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="F31" s="12">
-        <f>0.055*(Stage1A_Drainage!$F$136+Stage1B_Drainage!$F$42)</f>
-        <v>111747.0269275187</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B32" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="F32" s="31">
         <f>F31-F29</f>
-        <v>49185.776927518702</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+        <v>54942.739327518706</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F33" s="27">
         <f>F29/F31-1</f>
-        <v>-0.44015289068425556</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+        <v>-0.48193698879848257</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="23" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="4" t="s">
+      <c r="F36" s="9">
+        <f>0.18*(Stage1A_Drainage!$F$138+Stage1B_Drainage!$F$44)</f>
+        <v>373103.96507187939</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="F36" s="9">
-        <f>0.18*(Stage1A_Drainage!$F$136+Stage1B_Drainage!$F$42)</f>
-        <v>365717.5426718794</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="4" t="s">
-        <v>835</v>
       </c>
       <c r="C37" s="5">
         <v>6</v>
@@ -12678,13 +12814,13 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F38" s="9">
         <f>F36-F37</f>
-        <v>245717.5426718794</v>
+        <v>253103.96507187939</v>
       </c>
     </row>
   </sheetData>
